--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1359,6 +1359,4888 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128277319</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>547976</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6960165</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128277379</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98504</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>547929</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6960181</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128274290</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96595</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>547959</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6960358</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128284855</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>547938</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6960421</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128274733</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>547968</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6960276</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128274521</v>
+      </c>
+      <c r="B13" t="n">
+        <v>75145</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>308</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>547947</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6960412</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Betula</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128277304</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78787</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>547936</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6960173</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128277049</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92642</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>547985</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6960231</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128277341</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92642</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>547935</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6960188</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128284856</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78787</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>547952</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6960362</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128274594</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>548040</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6960306</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128273826</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>547957</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6960424</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128274743</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>548016</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6960300</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128277456</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92642</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>547921</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6960179</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128277198</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>547970</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6960207</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128284854</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78788</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>547936</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6960436</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128274886</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80133</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>548022</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6960304</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128273858</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>547952</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6960420</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128275378</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>548012</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6960292</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128278609</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>547984</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6960265</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128273941</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92642</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>547948</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6960398</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128274393</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>547975</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6960341</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128275283</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>547999</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6960288</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128274501</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>547975</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6960313</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128276953</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92636</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>548012</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6960292</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128274383</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92642</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>547964</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6960346</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128274414</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>547966</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6960356</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128277337</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>547930</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6960191</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128277041</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>547984</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6960265</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128277264</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80161</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>547947</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6960412</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128274387</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>548056</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6960360</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128274698</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>547997</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6960315</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128278639</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>547947</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6960412</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128274742</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>548022</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6960305</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128274083</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>547956</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6960372</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128274466</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>548066</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6960351</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128273967</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>547969</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6960411</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128277134</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>547979</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6960221</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128277422</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>548003</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6960256</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128274007</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>547955</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6960412</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128276966</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>548010</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6960276</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128277116</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>547993</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6960206</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128274041</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80160</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>547977</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6960396</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128277370</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>547938</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6960182</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128284858</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>547979</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6960273</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -2022,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128277304</v>
+        <v>128274594</v>
       </c>
       <c r="B14" t="n">
-        <v>78787</v>
+        <v>80132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,34 +2033,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547936</v>
+        <v>548040</v>
       </c>
       <c r="R14" t="n">
-        <v>6960173</v>
+        <v>6960306</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,60 +2117,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128277049</v>
+        <v>128284856</v>
       </c>
       <c r="B15" t="n">
-        <v>92642</v>
+        <v>78787</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547985</v>
+        <v>547952</v>
       </c>
       <c r="R15" t="n">
-        <v>6960231</v>
+        <v>6960362</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,44 +2224,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128277341</v>
+        <v>128277304</v>
       </c>
       <c r="B16" t="n">
-        <v>92642</v>
+        <v>78787</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547935</v>
+        <v>547936</v>
       </c>
       <c r="R16" t="n">
-        <v>6960188</v>
+        <v>6960173</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,60 +2331,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128284856</v>
+        <v>128277341</v>
       </c>
       <c r="B17" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547952</v>
+        <v>547935</v>
       </c>
       <c r="R17" t="n">
-        <v>6960362</v>
+        <v>6960188</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2438,44 +2438,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128274594</v>
+        <v>128277049</v>
       </c>
       <c r="B18" t="n">
-        <v>80132</v>
+        <v>92642</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548040</v>
+        <v>547985</v>
       </c>
       <c r="R18" t="n">
-        <v>6960306</v>
+        <v>6960231</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,12 +2545,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2888,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128277198</v>
+        <v>128284854</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>78788</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,42 +2899,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547970</v>
+        <v>547936</v>
       </c>
       <c r="R22" t="n">
-        <v>6960207</v>
+        <v>6960436</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2961,14 +2956,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2983,22 +2983,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128284854</v>
+        <v>128274886</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>80133</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,37 +3006,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547936</v>
+        <v>548022</v>
       </c>
       <c r="R23" t="n">
-        <v>6960436</v>
+        <v>6960304</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,22 +3090,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128274886</v>
+        <v>128277198</v>
       </c>
       <c r="B24" t="n">
-        <v>80133</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,34 +3113,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548022</v>
+        <v>547970</v>
       </c>
       <c r="R24" t="n">
-        <v>6960304</v>
+        <v>6960207</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3170,19 +3175,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:46</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3197,50 +3197,49 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128273858</v>
+        <v>128275378</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3249,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547952</v>
+        <v>548012</v>
       </c>
       <c r="R25" t="n">
-        <v>6960420</v>
+        <v>6960292</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3285,11 +3284,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3316,37 +3310,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128275378</v>
+        <v>128273858</v>
       </c>
       <c r="B26" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3355,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548012</v>
+        <v>547952</v>
       </c>
       <c r="R26" t="n">
-        <v>6960292</v>
+        <v>6960420</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3391,6 +3386,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3631,45 +3631,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128274393</v>
+        <v>128275283</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547975</v>
+        <v>547999</v>
       </c>
       <c r="R29" t="n">
-        <v>6960341</v>
+        <v>6960288</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3705,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3715,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,49 +3742,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128275283</v>
+        <v>128274393</v>
       </c>
       <c r="B30" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547999</v>
+        <v>547975</v>
       </c>
       <c r="R30" t="n">
-        <v>6960288</v>
+        <v>6960341</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4048,49 +4048,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128274383</v>
+        <v>128277337</v>
       </c>
       <c r="B33" t="n">
-        <v>92642</v>
+        <v>98470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547964</v>
+        <v>547930</v>
       </c>
       <c r="R33" t="n">
-        <v>6960346</v>
+        <v>6960191</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4120,9 +4120,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4137,19 +4147,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128274414</v>
+        <v>128277041</v>
       </c>
       <c r="B34" t="n">
         <v>98470</v>
@@ -4179,7 +4189,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4188,10 +4198,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547966</v>
+        <v>547984</v>
       </c>
       <c r="R34" t="n">
-        <v>6960356</v>
+        <v>6960265</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4223,7 +4233,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4233,7 +4243,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4260,7 +4270,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128277337</v>
+        <v>128274414</v>
       </c>
       <c r="B35" t="n">
         <v>98470</v>
@@ -4290,22 +4300,22 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547930</v>
+        <v>547966</v>
       </c>
       <c r="R35" t="n">
-        <v>6960191</v>
+        <v>6960356</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4334,7 +4344,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4344,7 +4354,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4359,49 +4369,49 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128277041</v>
+        <v>128277264</v>
       </c>
       <c r="B36" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4410,10 +4420,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547984</v>
+        <v>547947</v>
       </c>
       <c r="R36" t="n">
-        <v>6960265</v>
+        <v>6960412</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4445,7 +4455,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4455,7 +4465,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4466,26 +4476,51 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128277264</v>
+        <v>128274383</v>
       </c>
       <c r="B37" t="n">
-        <v>80161</v>
+        <v>92642</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4493,41 +4528,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547947</v>
+        <v>547964</v>
       </c>
       <c r="R37" t="n">
-        <v>6960412</v>
+        <v>6960346</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4554,21 +4589,11 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4577,79 +4602,53 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128274387</v>
+        <v>128278639</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4658,13 +4657,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548056</v>
+        <v>547947</v>
       </c>
       <c r="R38" t="n">
-        <v>6960360</v>
+        <v>6960412</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4693,7 +4692,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4703,12 +4702,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4719,16 +4713,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4846,37 +4845,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128278639</v>
+        <v>128274387</v>
       </c>
       <c r="B40" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>36</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4885,13 +4885,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547947</v>
+        <v>548056</v>
       </c>
       <c r="R40" t="n">
-        <v>6960412</v>
+        <v>6960360</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4930,7 +4930,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4941,21 +4946,16 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5069,10 +5069,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128274083</v>
+        <v>128273967</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5080,39 +5080,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>547956</v>
+        <v>547969</v>
       </c>
       <c r="R42" t="n">
-        <v>6960372</v>
+        <v>6960411</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5145,11 +5140,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5176,10 +5166,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128274466</v>
+        <v>128274083</v>
       </c>
       <c r="B43" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5187,34 +5177,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548066</v>
+        <v>547956</v>
       </c>
       <c r="R43" t="n">
-        <v>6960351</v>
+        <v>6960372</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5244,19 +5239,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:23</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5271,19 +5261,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128273967</v>
+        <v>128274466</v>
       </c>
       <c r="B44" t="n">
         <v>80132</v>
@@ -5314,14 +5304,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547969</v>
+        <v>548066</v>
       </c>
       <c r="R44" t="n">
-        <v>6960411</v>
+        <v>6960351</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5351,9 +5341,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5368,12 +5368,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6025,52 +6025,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128277370</v>
+        <v>128284858</v>
       </c>
       <c r="B51" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547938</v>
+        <v>547979</v>
       </c>
       <c r="R51" t="n">
-        <v>6960182</v>
+        <v>6960273</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6099,7 +6095,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6109,7 +6105,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6124,60 +6120,64 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128284858</v>
+        <v>128277370</v>
       </c>
       <c r="B52" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547979</v>
+        <v>547938</v>
       </c>
       <c r="R52" t="n">
-        <v>6960273</v>
+        <v>6960182</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6231,12 +6231,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -2343,7 +2343,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128277341</v>
+        <v>128277049</v>
       </c>
       <c r="B17" t="n">
         <v>92642</v>
@@ -2374,14 +2374,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547935</v>
+        <v>547985</v>
       </c>
       <c r="R17" t="n">
-        <v>6960188</v>
+        <v>6960231</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2438,19 +2438,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128277049</v>
+        <v>128277341</v>
       </c>
       <c r="B18" t="n">
         <v>92642</v>
@@ -2481,14 +2481,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547985</v>
+        <v>547935</v>
       </c>
       <c r="R18" t="n">
-        <v>6960231</v>
+        <v>6960188</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,12 +2545,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2674,45 +2674,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128274743</v>
+        <v>128277456</v>
       </c>
       <c r="B20" t="n">
-        <v>80132</v>
+        <v>92642</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548016</v>
+        <v>547921</v>
       </c>
       <c r="R20" t="n">
-        <v>6960300</v>
+        <v>6960179</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2769,57 +2769,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128277456</v>
+        <v>128274743</v>
       </c>
       <c r="B21" t="n">
-        <v>92642</v>
+        <v>80132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547921</v>
+        <v>548016</v>
       </c>
       <c r="R21" t="n">
-        <v>6960179</v>
+        <v>6960300</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2876,22 +2876,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128284854</v>
+        <v>128274886</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>80133</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,37 +2899,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547936</v>
+        <v>548022</v>
       </c>
       <c r="R22" t="n">
-        <v>6960436</v>
+        <v>6960304</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2983,22 +2983,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128274886</v>
+        <v>128284854</v>
       </c>
       <c r="B23" t="n">
-        <v>80133</v>
+        <v>78788</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,37 +3006,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548022</v>
+        <v>547936</v>
       </c>
       <c r="R23" t="n">
-        <v>6960304</v>
+        <v>6960436</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,12 +3090,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3631,49 +3631,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128275283</v>
+        <v>128274393</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547999</v>
+        <v>547975</v>
       </c>
       <c r="R29" t="n">
-        <v>6960288</v>
+        <v>6960341</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3705,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3715,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3742,10 +3738,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128274393</v>
+        <v>128276953</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>92636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3753,34 +3749,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547975</v>
+        <v>548012</v>
       </c>
       <c r="R30" t="n">
-        <v>6960341</v>
+        <v>6960292</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3810,19 +3806,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3837,12 +3823,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3951,45 +3937,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128276953</v>
+        <v>128275283</v>
       </c>
       <c r="B32" t="n">
-        <v>92636</v>
+        <v>98470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548012</v>
+        <v>547999</v>
       </c>
       <c r="R32" t="n">
-        <v>6960292</v>
+        <v>6960288</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4019,9 +4009,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,61 +4036,61 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128277337</v>
+        <v>128274383</v>
       </c>
       <c r="B33" t="n">
-        <v>98470</v>
+        <v>92642</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547930</v>
+        <v>547964</v>
       </c>
       <c r="R33" t="n">
-        <v>6960191</v>
+        <v>6960346</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4120,19 +4120,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4147,49 +4137,49 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128277041</v>
+        <v>128277264</v>
       </c>
       <c r="B34" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4198,10 +4188,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547984</v>
+        <v>547947</v>
       </c>
       <c r="R34" t="n">
-        <v>6960265</v>
+        <v>6960412</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4233,7 +4223,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4243,7 +4233,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4254,23 +4244,48 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128274414</v>
+        <v>128277337</v>
       </c>
       <c r="B35" t="n">
         <v>98470</v>
@@ -4300,22 +4315,22 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547966</v>
+        <v>547930</v>
       </c>
       <c r="R35" t="n">
-        <v>6960356</v>
+        <v>6960191</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4344,7 +4359,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4354,7 +4369,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4369,49 +4384,49 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128277264</v>
+        <v>128277041</v>
       </c>
       <c r="B36" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4420,10 +4435,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547947</v>
+        <v>547984</v>
       </c>
       <c r="R36" t="n">
-        <v>6960412</v>
+        <v>6960265</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4455,7 +4470,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4465,7 +4480,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4476,93 +4491,68 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128274383</v>
+        <v>128274414</v>
       </c>
       <c r="B37" t="n">
-        <v>92642</v>
+        <v>98470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547964</v>
+        <v>547966</v>
       </c>
       <c r="R37" t="n">
-        <v>6960346</v>
+        <v>6960356</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4589,9 +4579,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4606,12 +4606,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -2674,45 +2674,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128277456</v>
+        <v>128274743</v>
       </c>
       <c r="B20" t="n">
-        <v>92642</v>
+        <v>80132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547921</v>
+        <v>548016</v>
       </c>
       <c r="R20" t="n">
-        <v>6960179</v>
+        <v>6960300</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2769,57 +2769,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128274743</v>
+        <v>128277456</v>
       </c>
       <c r="B21" t="n">
-        <v>80132</v>
+        <v>92642</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548016</v>
+        <v>547921</v>
       </c>
       <c r="R21" t="n">
-        <v>6960300</v>
+        <v>6960179</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2876,12 +2876,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -5273,45 +5273,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128274466</v>
+        <v>128277134</v>
       </c>
       <c r="B44" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548066</v>
+        <v>547979</v>
       </c>
       <c r="R44" t="n">
-        <v>6960351</v>
+        <v>6960221</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5343,7 +5347,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5353,7 +5357,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5368,61 +5372,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128277134</v>
+        <v>128274466</v>
       </c>
       <c r="B45" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547979</v>
+        <v>548066</v>
       </c>
       <c r="R45" t="n">
-        <v>6960221</v>
+        <v>6960351</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5479,12 +5479,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -2674,45 +2674,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128274743</v>
+        <v>128277456</v>
       </c>
       <c r="B20" t="n">
-        <v>80132</v>
+        <v>92642</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548016</v>
+        <v>547921</v>
       </c>
       <c r="R20" t="n">
-        <v>6960300</v>
+        <v>6960179</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2769,57 +2769,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128277456</v>
+        <v>128274743</v>
       </c>
       <c r="B21" t="n">
-        <v>92642</v>
+        <v>80132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547921</v>
+        <v>548016</v>
       </c>
       <c r="R21" t="n">
-        <v>6960179</v>
+        <v>6960300</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2876,12 +2876,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3209,37 +3209,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128275378</v>
+        <v>128273858</v>
       </c>
       <c r="B25" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3248,10 +3249,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548012</v>
+        <v>547952</v>
       </c>
       <c r="R25" t="n">
-        <v>6960292</v>
+        <v>6960420</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3284,6 +3285,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3310,38 +3316,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128273858</v>
+        <v>128275378</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3350,10 +3355,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547952</v>
+        <v>548012</v>
       </c>
       <c r="R26" t="n">
-        <v>6960420</v>
+        <v>6960292</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3386,11 +3391,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -5273,49 +5273,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128277134</v>
+        <v>128274466</v>
       </c>
       <c r="B44" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547979</v>
+        <v>548066</v>
       </c>
       <c r="R44" t="n">
-        <v>6960221</v>
+        <v>6960351</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5347,7 +5343,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5357,7 +5353,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5372,57 +5368,61 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128274466</v>
+        <v>128277134</v>
       </c>
       <c r="B45" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548066</v>
+        <v>547979</v>
       </c>
       <c r="R45" t="n">
-        <v>6960351</v>
+        <v>6960221</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5479,12 +5479,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6025,48 +6025,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128284858</v>
+        <v>128277370</v>
       </c>
       <c r="B51" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547979</v>
+        <v>547938</v>
       </c>
       <c r="R51" t="n">
-        <v>6960273</v>
+        <v>6960182</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6095,7 +6099,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6105,7 +6109,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6120,64 +6124,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128277370</v>
+        <v>128284858</v>
       </c>
       <c r="B52" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547938</v>
+        <v>547979</v>
       </c>
       <c r="R52" t="n">
-        <v>6960182</v>
+        <v>6960273</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6231,12 +6231,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -2343,7 +2343,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128277049</v>
+        <v>128277341</v>
       </c>
       <c r="B17" t="n">
         <v>92642</v>
@@ -2374,14 +2374,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547985</v>
+        <v>547935</v>
       </c>
       <c r="R17" t="n">
-        <v>6960231</v>
+        <v>6960188</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2438,19 +2438,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128277341</v>
+        <v>128277049</v>
       </c>
       <c r="B18" t="n">
         <v>92642</v>
@@ -2481,14 +2481,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547935</v>
+        <v>547985</v>
       </c>
       <c r="R18" t="n">
-        <v>6960188</v>
+        <v>6960231</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,12 +2545,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3631,45 +3631,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128274393</v>
+        <v>128275283</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547975</v>
+        <v>547999</v>
       </c>
       <c r="R29" t="n">
-        <v>6960341</v>
+        <v>6960288</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3705,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3715,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,10 +3742,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128276953</v>
+        <v>128274393</v>
       </c>
       <c r="B30" t="n">
-        <v>92636</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,34 +3753,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548012</v>
+        <v>547975</v>
       </c>
       <c r="R30" t="n">
-        <v>6960292</v>
+        <v>6960341</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3806,9 +3810,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3823,12 +3837,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3937,49 +3951,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128275283</v>
+        <v>128276953</v>
       </c>
       <c r="B32" t="n">
-        <v>98470</v>
+        <v>92636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547999</v>
+        <v>548012</v>
       </c>
       <c r="R32" t="n">
-        <v>6960288</v>
+        <v>6960292</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4009,19 +4019,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,61 +4036,61 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128274383</v>
+        <v>128277337</v>
       </c>
       <c r="B33" t="n">
-        <v>92642</v>
+        <v>98470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547964</v>
+        <v>547930</v>
       </c>
       <c r="R33" t="n">
-        <v>6960346</v>
+        <v>6960191</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4120,9 +4120,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4137,49 +4147,49 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128277264</v>
+        <v>128277041</v>
       </c>
       <c r="B34" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4188,10 +4198,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547947</v>
+        <v>547984</v>
       </c>
       <c r="R34" t="n">
-        <v>6960412</v>
+        <v>6960265</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4223,7 +4233,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4233,7 +4243,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4244,48 +4254,23 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128277337</v>
+        <v>128274414</v>
       </c>
       <c r="B35" t="n">
         <v>98470</v>
@@ -4315,22 +4300,22 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547930</v>
+        <v>547966</v>
       </c>
       <c r="R35" t="n">
-        <v>6960191</v>
+        <v>6960356</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4359,7 +4344,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4369,7 +4354,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4384,49 +4369,49 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128277041</v>
+        <v>128277264</v>
       </c>
       <c r="B36" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4435,10 +4420,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547984</v>
+        <v>547947</v>
       </c>
       <c r="R36" t="n">
-        <v>6960265</v>
+        <v>6960412</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4470,7 +4455,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4480,7 +4465,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4491,68 +4476,93 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128274414</v>
+        <v>128274383</v>
       </c>
       <c r="B37" t="n">
-        <v>98470</v>
+        <v>92642</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547966</v>
+        <v>547964</v>
       </c>
       <c r="R37" t="n">
-        <v>6960356</v>
+        <v>6960346</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4579,19 +4589,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4606,12 +4606,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -6025,52 +6025,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128277370</v>
+        <v>128284858</v>
       </c>
       <c r="B51" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547938</v>
+        <v>547979</v>
       </c>
       <c r="R51" t="n">
-        <v>6960182</v>
+        <v>6960273</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6099,7 +6095,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6109,7 +6105,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6124,60 +6120,64 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128284858</v>
+        <v>128277370</v>
       </c>
       <c r="B52" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547979</v>
+        <v>547938</v>
       </c>
       <c r="R52" t="n">
-        <v>6960273</v>
+        <v>6960182</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6231,12 +6231,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -2343,7 +2343,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128277341</v>
+        <v>128277049</v>
       </c>
       <c r="B17" t="n">
         <v>92642</v>
@@ -2374,14 +2374,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547935</v>
+        <v>547985</v>
       </c>
       <c r="R17" t="n">
-        <v>6960188</v>
+        <v>6960231</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2438,19 +2438,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128277049</v>
+        <v>128277341</v>
       </c>
       <c r="B18" t="n">
         <v>92642</v>
@@ -2481,14 +2481,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547985</v>
+        <v>547935</v>
       </c>
       <c r="R18" t="n">
-        <v>6960231</v>
+        <v>6960188</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,12 +2545,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3209,38 +3209,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128273858</v>
+        <v>128275378</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3249,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547952</v>
+        <v>548012</v>
       </c>
       <c r="R25" t="n">
-        <v>6960420</v>
+        <v>6960292</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3285,11 +3284,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3316,37 +3310,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128275378</v>
+        <v>128273858</v>
       </c>
       <c r="B26" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3355,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548012</v>
+        <v>547952</v>
       </c>
       <c r="R26" t="n">
-        <v>6960292</v>
+        <v>6960420</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3391,6 +3386,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3631,49 +3631,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128275283</v>
+        <v>128274393</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547999</v>
+        <v>547975</v>
       </c>
       <c r="R29" t="n">
-        <v>6960288</v>
+        <v>6960341</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3705,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3715,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3742,10 +3738,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128274393</v>
+        <v>128276953</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>92636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3753,34 +3749,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547975</v>
+        <v>548012</v>
       </c>
       <c r="R30" t="n">
-        <v>6960341</v>
+        <v>6960292</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3810,19 +3806,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3837,12 +3823,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3951,45 +3937,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128276953</v>
+        <v>128275283</v>
       </c>
       <c r="B32" t="n">
-        <v>92636</v>
+        <v>98470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548012</v>
+        <v>547999</v>
       </c>
       <c r="R32" t="n">
-        <v>6960292</v>
+        <v>6960288</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4019,9 +4009,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,12 +4036,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -6025,48 +6025,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128284858</v>
+        <v>128277370</v>
       </c>
       <c r="B51" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547979</v>
+        <v>547938</v>
       </c>
       <c r="R51" t="n">
-        <v>6960273</v>
+        <v>6960182</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6095,7 +6099,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6105,7 +6109,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6120,64 +6124,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128277370</v>
+        <v>128284858</v>
       </c>
       <c r="B52" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547938</v>
+        <v>547979</v>
       </c>
       <c r="R52" t="n">
-        <v>6960182</v>
+        <v>6960273</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6231,12 +6231,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -1779,10 +1779,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128274733</v>
+        <v>128274521</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>75145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,42 +1790,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547968</v>
+        <v>547947</v>
       </c>
       <c r="R12" t="n">
-        <v>6960276</v>
+        <v>6960412</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,14 +1851,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,26 +1874,51 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128274521</v>
+        <v>128274733</v>
       </c>
       <c r="B13" t="n">
-        <v>75145</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,41 +1926,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547947</v>
+        <v>547968</v>
       </c>
       <c r="R13" t="n">
-        <v>6960412</v>
+        <v>6960276</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1958,19 +1988,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:26</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1981,41 +2006,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2343,7 +2343,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128277049</v>
+        <v>128277341</v>
       </c>
       <c r="B17" t="n">
         <v>92642</v>
@@ -2374,14 +2374,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547985</v>
+        <v>547935</v>
       </c>
       <c r="R17" t="n">
-        <v>6960231</v>
+        <v>6960188</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2438,19 +2438,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128277341</v>
+        <v>128277049</v>
       </c>
       <c r="B18" t="n">
         <v>92642</v>
@@ -2481,14 +2481,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547935</v>
+        <v>547985</v>
       </c>
       <c r="R18" t="n">
-        <v>6960188</v>
+        <v>6960231</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,12 +2545,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2888,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128274886</v>
+        <v>128284854</v>
       </c>
       <c r="B22" t="n">
-        <v>80133</v>
+        <v>78788</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,37 +2899,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548022</v>
+        <v>547936</v>
       </c>
       <c r="R22" t="n">
-        <v>6960304</v>
+        <v>6960436</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2983,22 +2983,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128284854</v>
+        <v>128274886</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>80133</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,37 +3006,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547936</v>
+        <v>548022</v>
       </c>
       <c r="R23" t="n">
-        <v>6960436</v>
+        <v>6960304</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,12 +3090,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3631,45 +3631,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128274393</v>
+        <v>128275283</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547975</v>
+        <v>547999</v>
       </c>
       <c r="R29" t="n">
-        <v>6960341</v>
+        <v>6960288</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3705,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3715,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,10 +3742,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128276953</v>
+        <v>128274393</v>
       </c>
       <c r="B30" t="n">
-        <v>92636</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,34 +3753,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548012</v>
+        <v>547975</v>
       </c>
       <c r="R30" t="n">
-        <v>6960292</v>
+        <v>6960341</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3806,9 +3810,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3823,12 +3837,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3937,49 +3951,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128275283</v>
+        <v>128276953</v>
       </c>
       <c r="B32" t="n">
-        <v>98470</v>
+        <v>92636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547999</v>
+        <v>548012</v>
       </c>
       <c r="R32" t="n">
-        <v>6960288</v>
+        <v>6960292</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4009,19 +4019,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,12 +4036,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -6025,52 +6025,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128277370</v>
+        <v>128284858</v>
       </c>
       <c r="B51" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547938</v>
+        <v>547979</v>
       </c>
       <c r="R51" t="n">
-        <v>6960182</v>
+        <v>6960273</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6099,7 +6095,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6109,7 +6105,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6124,60 +6120,64 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128284858</v>
+        <v>128277370</v>
       </c>
       <c r="B52" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547979</v>
+        <v>547938</v>
       </c>
       <c r="R52" t="n">
-        <v>6960273</v>
+        <v>6960182</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6231,12 +6231,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -1364,7 +1364,7 @@
         <v>128277319</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>128277379</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>98512</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>128274290</v>
       </c>
       <c r="B10" t="n">
-        <v>96595</v>
+        <v>96603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>128284855</v>
       </c>
       <c r="B11" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>128274521</v>
       </c>
       <c r="B12" t="n">
-        <v>75145</v>
+        <v>75148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>128274733</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>128274594</v>
       </c>
       <c r="B14" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>128284856</v>
       </c>
       <c r="B15" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>128277304</v>
       </c>
       <c r="B16" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,45 +2343,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128277341</v>
+        <v>128273826</v>
       </c>
       <c r="B17" t="n">
-        <v>92642</v>
+        <v>57673</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547935</v>
+        <v>547957</v>
       </c>
       <c r="R17" t="n">
-        <v>6960188</v>
+        <v>6960424</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,7 +2418,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2428,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128277049</v>
+        <v>128277341</v>
       </c>
       <c r="B18" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2481,14 +2491,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547985</v>
+        <v>547935</v>
       </c>
       <c r="R18" t="n">
-        <v>6960231</v>
+        <v>6960188</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,7 +2530,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2540,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,62 +2555,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128273826</v>
+        <v>128277049</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>92650</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547957</v>
+        <v>547985</v>
       </c>
       <c r="R19" t="n">
-        <v>6960424</v>
+        <v>6960231</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2637,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,12 +2647,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2662,57 +2662,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128277456</v>
+        <v>128274743</v>
       </c>
       <c r="B20" t="n">
-        <v>92642</v>
+        <v>80135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547921</v>
+        <v>548016</v>
       </c>
       <c r="R20" t="n">
-        <v>6960179</v>
+        <v>6960300</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2769,57 +2769,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128274743</v>
+        <v>128277456</v>
       </c>
       <c r="B21" t="n">
-        <v>80132</v>
+        <v>92650</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548016</v>
+        <v>547921</v>
       </c>
       <c r="R21" t="n">
-        <v>6960300</v>
+        <v>6960179</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2876,22 +2876,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128284854</v>
+        <v>128277198</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>57673</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,37 +2899,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547936</v>
+        <v>547970</v>
       </c>
       <c r="R22" t="n">
-        <v>6960436</v>
+        <v>6960207</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2956,19 +2961,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:56</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2983,12 +2983,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2998,7 +2998,7 @@
         <v>128274886</v>
       </c>
       <c r="B23" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3102,10 +3102,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128277198</v>
+        <v>128284854</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>78791</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,42 +3113,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547970</v>
+        <v>547936</v>
       </c>
       <c r="R24" t="n">
-        <v>6960207</v>
+        <v>6960436</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3175,14 +3170,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3197,49 +3197,50 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128275378</v>
+        <v>128273858</v>
       </c>
       <c r="B25" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3248,10 +3249,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548012</v>
+        <v>547952</v>
       </c>
       <c r="R25" t="n">
-        <v>6960292</v>
+        <v>6960420</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3284,6 +3285,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3310,38 +3316,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128273858</v>
+        <v>128275378</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3350,10 +3355,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547952</v>
+        <v>548012</v>
       </c>
       <c r="R26" t="n">
-        <v>6960420</v>
+        <v>6960292</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3386,11 +3391,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3420,7 +3420,7 @@
         <v>128278609</v>
       </c>
       <c r="B27" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128273941</v>
       </c>
       <c r="B28" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3631,49 +3631,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128275283</v>
+        <v>128276953</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>92644</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547999</v>
+        <v>548012</v>
       </c>
       <c r="R29" t="n">
-        <v>6960288</v>
+        <v>6960292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3703,19 +3699,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3730,12 +3716,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3745,7 +3731,7 @@
         <v>128274393</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3849,50 +3835,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128274501</v>
+        <v>128275283</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>547975</v>
+        <v>547999</v>
       </c>
       <c r="R31" t="n">
-        <v>6960313</v>
+        <v>6960288</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3922,9 +3907,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3939,22 +3934,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128276953</v>
+        <v>128274501</v>
       </c>
       <c r="B32" t="n">
-        <v>92636</v>
+        <v>57673</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3962,34 +3957,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548012</v>
+        <v>547975</v>
       </c>
       <c r="R32" t="n">
-        <v>6960292</v>
+        <v>6960313</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4051,7 +4051,7 @@
         <v>128277337</v>
       </c>
       <c r="B33" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>128277041</v>
       </c>
       <c r="B34" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>128274414</v>
       </c>
       <c r="B35" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>128277264</v>
       </c>
       <c r="B36" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>128274383</v>
       </c>
       <c r="B37" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4618,37 +4618,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128278639</v>
+        <v>128274387</v>
       </c>
       <c r="B38" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>36</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4657,13 +4658,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>547947</v>
+        <v>548056</v>
       </c>
       <c r="R38" t="n">
-        <v>6960412</v>
+        <v>6960360</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4692,7 +4693,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4702,7 +4703,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4713,31 +4719,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128274698</v>
+        <v>128278639</v>
       </c>
       <c r="B39" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4764,7 +4765,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>36</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4773,13 +4774,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>547997</v>
+        <v>547947</v>
       </c>
       <c r="R39" t="n">
-        <v>6960315</v>
+        <v>6960412</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4808,7 +4809,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4818,7 +4819,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4829,54 +4830,58 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128274387</v>
+        <v>128274698</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4885,10 +4890,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548056</v>
+        <v>547997</v>
       </c>
       <c r="R40" t="n">
-        <v>6960360</v>
+        <v>6960315</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4920,7 +4925,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4930,12 +4935,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4950,12 +4950,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4965,7 +4965,7 @@
         <v>128274742</v>
       </c>
       <c r="B41" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5069,10 +5069,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128273967</v>
+        <v>128274083</v>
       </c>
       <c r="B42" t="n">
-        <v>80132</v>
+        <v>57673</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5080,34 +5080,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>547969</v>
+        <v>547956</v>
       </c>
       <c r="R42" t="n">
-        <v>6960411</v>
+        <v>6960372</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5140,6 +5145,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5166,50 +5176,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128274083</v>
+        <v>128277134</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547956</v>
+        <v>547979</v>
       </c>
       <c r="R43" t="n">
-        <v>6960372</v>
+        <v>6960221</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5239,14 +5248,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5261,22 +5275,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128274466</v>
+        <v>128273967</v>
       </c>
       <c r="B44" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5304,14 +5318,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548066</v>
+        <v>547969</v>
       </c>
       <c r="R44" t="n">
-        <v>6960351</v>
+        <v>6960411</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5341,19 +5355,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5368,61 +5372,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128277134</v>
+        <v>128274466</v>
       </c>
       <c r="B45" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547979</v>
+        <v>548066</v>
       </c>
       <c r="R45" t="n">
-        <v>6960221</v>
+        <v>6960351</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5479,12 +5479,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5494,7 +5494,7 @@
         <v>128277422</v>
       </c>
       <c r="B46" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,37 +5593,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128274007</v>
+        <v>128276966</v>
       </c>
       <c r="B47" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5632,10 +5633,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547955</v>
+        <v>548010</v>
       </c>
       <c r="R47" t="n">
-        <v>6960412</v>
+        <v>6960276</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5667,7 +5668,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5677,7 +5678,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5692,50 +5698,49 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128276966</v>
+        <v>128274007</v>
       </c>
       <c r="B48" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5744,10 +5749,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548010</v>
+        <v>547955</v>
       </c>
       <c r="R48" t="n">
-        <v>6960276</v>
+        <v>6960412</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5779,7 +5784,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5789,12 +5794,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5809,12 +5809,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5824,7 +5824,7 @@
         <v>128277116</v>
       </c>
       <c r="B49" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128274041</v>
       </c>
       <c r="B50" t="n">
-        <v>80160</v>
+        <v>80163</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>128284858</v>
       </c>
       <c r="B51" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>128277370</v>
       </c>
       <c r="B52" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -2888,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128277198</v>
+        <v>128274886</v>
       </c>
       <c r="B22" t="n">
-        <v>57673</v>
+        <v>80136</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,39 +2899,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547970</v>
+        <v>548022</v>
       </c>
       <c r="R22" t="n">
-        <v>6960207</v>
+        <v>6960304</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2961,14 +2956,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2983,22 +2983,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128274886</v>
+        <v>128277198</v>
       </c>
       <c r="B23" t="n">
-        <v>80136</v>
+        <v>57673</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,34 +3006,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548022</v>
+        <v>547970</v>
       </c>
       <c r="R23" t="n">
-        <v>6960304</v>
+        <v>6960207</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3063,19 +3068,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:46</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,12 +3090,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4048,49 +4048,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128277337</v>
+        <v>128274383</v>
       </c>
       <c r="B33" t="n">
-        <v>98478</v>
+        <v>92650</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547930</v>
+        <v>547964</v>
       </c>
       <c r="R33" t="n">
-        <v>6960191</v>
+        <v>6960346</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4120,19 +4120,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4147,49 +4137,49 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128277041</v>
+        <v>128277264</v>
       </c>
       <c r="B34" t="n">
-        <v>98478</v>
+        <v>80164</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4198,10 +4188,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547984</v>
+        <v>547947</v>
       </c>
       <c r="R34" t="n">
-        <v>6960265</v>
+        <v>6960412</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4233,7 +4223,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4243,7 +4233,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4254,23 +4244,48 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128274414</v>
+        <v>128277337</v>
       </c>
       <c r="B35" t="n">
         <v>98478</v>
@@ -4300,22 +4315,22 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547966</v>
+        <v>547930</v>
       </c>
       <c r="R35" t="n">
-        <v>6960356</v>
+        <v>6960191</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4344,7 +4359,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4354,7 +4369,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4369,49 +4384,49 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128277264</v>
+        <v>128277041</v>
       </c>
       <c r="B36" t="n">
-        <v>80164</v>
+        <v>98478</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4420,10 +4435,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547947</v>
+        <v>547984</v>
       </c>
       <c r="R36" t="n">
-        <v>6960412</v>
+        <v>6960265</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4455,7 +4470,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4465,7 +4480,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4476,93 +4491,68 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128274383</v>
+        <v>128274414</v>
       </c>
       <c r="B37" t="n">
-        <v>92650</v>
+        <v>98478</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547964</v>
+        <v>547966</v>
       </c>
       <c r="R37" t="n">
-        <v>6960346</v>
+        <v>6960356</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4589,9 +4579,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4606,12 +4606,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -6025,48 +6025,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128284858</v>
+        <v>128277370</v>
       </c>
       <c r="B51" t="n">
-        <v>80135</v>
+        <v>98478</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547979</v>
+        <v>547938</v>
       </c>
       <c r="R51" t="n">
-        <v>6960273</v>
+        <v>6960182</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6095,7 +6099,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6105,7 +6109,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6120,64 +6124,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128277370</v>
+        <v>128284858</v>
       </c>
       <c r="B52" t="n">
-        <v>98478</v>
+        <v>80135</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547938</v>
+        <v>547979</v>
       </c>
       <c r="R52" t="n">
-        <v>6960182</v>
+        <v>6960273</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6231,12 +6231,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -1364,7 +1364,7 @@
         <v>128277319</v>
       </c>
       <c r="B8" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>128277379</v>
       </c>
       <c r="B9" t="n">
-        <v>98512</v>
+        <v>98605</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>128274290</v>
       </c>
       <c r="B10" t="n">
-        <v>96603</v>
+        <v>96696</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>128284855</v>
       </c>
       <c r="B11" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128274521</v>
+        <v>128274733</v>
       </c>
       <c r="B12" t="n">
-        <v>75148</v>
+        <v>57685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,41 +1790,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547947</v>
+        <v>547968</v>
       </c>
       <c r="R12" t="n">
-        <v>6960412</v>
+        <v>6960276</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,19 +1852,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:26</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,51 +1870,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128274733</v>
+        <v>128274521</v>
       </c>
       <c r="B13" t="n">
-        <v>57673</v>
+        <v>75163</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1926,42 +1897,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547968</v>
+        <v>547947</v>
       </c>
       <c r="R13" t="n">
-        <v>6960276</v>
+        <v>6960412</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1988,14 +1958,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,48 +1981,73 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128274594</v>
+        <v>128277049</v>
       </c>
       <c r="B14" t="n">
-        <v>80135</v>
+        <v>92742</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548040</v>
+        <v>547985</v>
       </c>
       <c r="R14" t="n">
-        <v>6960306</v>
+        <v>6960231</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,60 +2117,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128284856</v>
+        <v>128277341</v>
       </c>
       <c r="B15" t="n">
-        <v>78790</v>
+        <v>92742</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547952</v>
+        <v>547935</v>
       </c>
       <c r="R15" t="n">
-        <v>6960362</v>
+        <v>6960188</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,22 +2224,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128277304</v>
+        <v>128284856</v>
       </c>
       <c r="B16" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,17 +2267,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547936</v>
+        <v>547952</v>
       </c>
       <c r="R16" t="n">
-        <v>6960173</v>
+        <v>6960362</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2331,22 +2331,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128273826</v>
+        <v>128277304</v>
       </c>
       <c r="B17" t="n">
-        <v>57673</v>
+        <v>78840</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,39 +2354,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547957</v>
+        <v>547936</v>
       </c>
       <c r="R17" t="n">
-        <v>6960424</v>
+        <v>6960173</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2428,12 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2448,57 +2438,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128277341</v>
+        <v>128274594</v>
       </c>
       <c r="B18" t="n">
-        <v>92650</v>
+        <v>80188</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547935</v>
+        <v>548040</v>
       </c>
       <c r="R18" t="n">
-        <v>6960188</v>
+        <v>6960306</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2530,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2540,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2567,45 +2557,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128277049</v>
+        <v>128273826</v>
       </c>
       <c r="B19" t="n">
-        <v>92650</v>
+        <v>57685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547985</v>
+        <v>547957</v>
       </c>
       <c r="R19" t="n">
-        <v>6960231</v>
+        <v>6960424</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2637,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2647,7 +2642,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2662,57 +2662,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128274743</v>
+        <v>128277456</v>
       </c>
       <c r="B20" t="n">
-        <v>80135</v>
+        <v>92742</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548016</v>
+        <v>547921</v>
       </c>
       <c r="R20" t="n">
-        <v>6960300</v>
+        <v>6960179</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2769,57 +2769,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128277456</v>
+        <v>128274743</v>
       </c>
       <c r="B21" t="n">
-        <v>92650</v>
+        <v>80188</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547921</v>
+        <v>548016</v>
       </c>
       <c r="R21" t="n">
-        <v>6960179</v>
+        <v>6960300</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2876,22 +2876,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128274886</v>
+        <v>128277198</v>
       </c>
       <c r="B22" t="n">
-        <v>80136</v>
+        <v>57685</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,34 +2899,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548022</v>
+        <v>547970</v>
       </c>
       <c r="R22" t="n">
-        <v>6960304</v>
+        <v>6960207</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2956,19 +2961,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:46</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2983,22 +2983,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128277198</v>
+        <v>128274886</v>
       </c>
       <c r="B23" t="n">
-        <v>57673</v>
+        <v>80189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,39 +3006,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547970</v>
+        <v>548022</v>
       </c>
       <c r="R23" t="n">
-        <v>6960207</v>
+        <v>6960304</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3068,14 +3063,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,12 +3090,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
         <v>128284854</v>
       </c>
       <c r="B24" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3209,38 +3209,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128273858</v>
+        <v>128275378</v>
       </c>
       <c r="B25" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3249,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547952</v>
+        <v>548012</v>
       </c>
       <c r="R25" t="n">
-        <v>6960420</v>
+        <v>6960292</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3285,11 +3284,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3316,37 +3310,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128275378</v>
+        <v>128273858</v>
       </c>
       <c r="B26" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3355,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548012</v>
+        <v>547952</v>
       </c>
       <c r="R26" t="n">
-        <v>6960292</v>
+        <v>6960420</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3391,6 +3386,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3420,7 +3420,7 @@
         <v>128278609</v>
       </c>
       <c r="B27" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128273941</v>
       </c>
       <c r="B28" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3631,45 +3631,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128276953</v>
+        <v>128275283</v>
       </c>
       <c r="B29" t="n">
-        <v>92644</v>
+        <v>98571</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548012</v>
+        <v>547999</v>
       </c>
       <c r="R29" t="n">
-        <v>6960292</v>
+        <v>6960288</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3699,9 +3703,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3716,22 +3730,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128274393</v>
+        <v>128276953</v>
       </c>
       <c r="B30" t="n">
-        <v>79032</v>
+        <v>92736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3739,34 +3753,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547975</v>
+        <v>548012</v>
       </c>
       <c r="R30" t="n">
-        <v>6960341</v>
+        <v>6960292</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3796,19 +3810,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3823,61 +3827,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128275283</v>
+        <v>128274393</v>
       </c>
       <c r="B31" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>547999</v>
+        <v>547975</v>
       </c>
       <c r="R31" t="n">
-        <v>6960288</v>
+        <v>6960341</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3949,7 +3949,7 @@
         <v>128274501</v>
       </c>
       <c r="B32" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>128274383</v>
       </c>
       <c r="B33" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>128277264</v>
       </c>
       <c r="B34" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128277337</v>
+        <v>128274414</v>
       </c>
       <c r="B35" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4315,22 +4315,22 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547930</v>
+        <v>547966</v>
       </c>
       <c r="R35" t="n">
-        <v>6960191</v>
+        <v>6960356</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4384,12 +4384,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4399,7 +4399,7 @@
         <v>128277041</v>
       </c>
       <c r="B36" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4507,10 +4507,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128274414</v>
+        <v>128277337</v>
       </c>
       <c r="B37" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4537,22 +4537,22 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547966</v>
+        <v>547930</v>
       </c>
       <c r="R37" t="n">
-        <v>6960356</v>
+        <v>6960191</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4606,50 +4606,49 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128274387</v>
+        <v>128274698</v>
       </c>
       <c r="B38" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4658,10 +4657,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548056</v>
+        <v>547997</v>
       </c>
       <c r="R38" t="n">
-        <v>6960360</v>
+        <v>6960315</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4693,7 +4692,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4703,12 +4702,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4723,12 +4717,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4738,7 +4732,7 @@
         <v>128278639</v>
       </c>
       <c r="B39" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4851,37 +4845,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128274698</v>
+        <v>128274387</v>
       </c>
       <c r="B40" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4890,10 +4885,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547997</v>
+        <v>548056</v>
       </c>
       <c r="R40" t="n">
-        <v>6960315</v>
+        <v>6960360</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4925,7 +4920,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4935,7 +4930,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4950,12 +4950,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4965,7 +4965,7 @@
         <v>128274742</v>
       </c>
       <c r="B41" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5069,10 +5069,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128274083</v>
+        <v>128273967</v>
       </c>
       <c r="B42" t="n">
-        <v>57673</v>
+        <v>80188</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5080,39 +5080,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>547956</v>
+        <v>547969</v>
       </c>
       <c r="R42" t="n">
-        <v>6960372</v>
+        <v>6960411</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5145,11 +5140,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5176,49 +5166,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128277134</v>
+        <v>128274466</v>
       </c>
       <c r="B43" t="n">
-        <v>98478</v>
+        <v>80188</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547979</v>
+        <v>548066</v>
       </c>
       <c r="R43" t="n">
-        <v>6960221</v>
+        <v>6960351</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5250,7 +5236,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5260,7 +5246,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5275,22 +5261,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128273967</v>
+        <v>128274083</v>
       </c>
       <c r="B44" t="n">
-        <v>80135</v>
+        <v>57685</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5298,34 +5284,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547969</v>
+        <v>547956</v>
       </c>
       <c r="R44" t="n">
-        <v>6960411</v>
+        <v>6960372</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5358,6 +5349,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5384,45 +5380,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128274466</v>
+        <v>128277134</v>
       </c>
       <c r="B45" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548066</v>
+        <v>547979</v>
       </c>
       <c r="R45" t="n">
-        <v>6960351</v>
+        <v>6960221</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5479,12 +5479,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5494,7 +5494,7 @@
         <v>128277422</v>
       </c>
       <c r="B46" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,38 +5593,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128276966</v>
+        <v>128274007</v>
       </c>
       <c r="B47" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5633,10 +5632,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548010</v>
+        <v>547955</v>
       </c>
       <c r="R47" t="n">
-        <v>6960276</v>
+        <v>6960412</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5668,7 +5667,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5678,12 +5677,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5698,49 +5692,50 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128274007</v>
+        <v>128276966</v>
       </c>
       <c r="B48" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5749,10 +5744,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547955</v>
+        <v>548010</v>
       </c>
       <c r="R48" t="n">
-        <v>6960412</v>
+        <v>6960276</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5784,7 +5779,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5794,7 +5789,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5809,12 +5809,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5824,7 +5824,7 @@
         <v>128277116</v>
       </c>
       <c r="B49" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128274041</v>
       </c>
       <c r="B50" t="n">
-        <v>80163</v>
+        <v>80216</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>128277370</v>
       </c>
       <c r="B51" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>128284858</v>
       </c>
       <c r="B52" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,48 +1575,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128274290</v>
+        <v>128284855</v>
       </c>
       <c r="B10" t="n">
-        <v>96696</v>
+        <v>80188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547959</v>
+        <v>547938</v>
       </c>
       <c r="R10" t="n">
-        <v>6960358</v>
+        <v>6960421</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1643,9 +1643,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,60 +1670,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128284855</v>
+        <v>128274290</v>
       </c>
       <c r="B11" t="n">
-        <v>80188</v>
+        <v>96696</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547938</v>
+        <v>547959</v>
       </c>
       <c r="R11" t="n">
-        <v>6960421</v>
+        <v>6960358</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,19 +1750,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,12 +1767,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128277049</v>
+        <v>128277341</v>
       </c>
       <c r="B14" t="n">
         <v>92742</v>
@@ -2053,14 +2053,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547985</v>
+        <v>547935</v>
       </c>
       <c r="R14" t="n">
-        <v>6960231</v>
+        <v>6960188</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,19 +2117,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128277341</v>
+        <v>128277049</v>
       </c>
       <c r="B15" t="n">
         <v>92742</v>
@@ -2160,14 +2160,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547935</v>
+        <v>547985</v>
       </c>
       <c r="R15" t="n">
-        <v>6960188</v>
+        <v>6960231</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,22 +2224,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128284856</v>
+        <v>128274594</v>
       </c>
       <c r="B16" t="n">
-        <v>78840</v>
+        <v>80188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,37 +2247,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547952</v>
+        <v>548040</v>
       </c>
       <c r="R16" t="n">
-        <v>6960362</v>
+        <v>6960306</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2331,19 +2331,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128277304</v>
+        <v>128284856</v>
       </c>
       <c r="B17" t="n">
         <v>78840</v>
@@ -2374,17 +2374,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547936</v>
+        <v>547952</v>
       </c>
       <c r="R17" t="n">
-        <v>6960173</v>
+        <v>6960362</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2438,22 +2438,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128274594</v>
+        <v>128277304</v>
       </c>
       <c r="B18" t="n">
-        <v>80188</v>
+        <v>78840</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,34 +2461,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548040</v>
+        <v>547936</v>
       </c>
       <c r="R18" t="n">
-        <v>6960306</v>
+        <v>6960173</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,12 +2545,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3209,37 +3209,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128275378</v>
+        <v>128273858</v>
       </c>
       <c r="B25" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3248,10 +3249,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548012</v>
+        <v>547952</v>
       </c>
       <c r="R25" t="n">
-        <v>6960292</v>
+        <v>6960420</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3284,6 +3285,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3310,38 +3316,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128273858</v>
+        <v>128275378</v>
       </c>
       <c r="B26" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3350,10 +3355,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547952</v>
+        <v>548012</v>
       </c>
       <c r="R26" t="n">
-        <v>6960420</v>
+        <v>6960292</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3386,11 +3391,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3631,49 +3631,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128275283</v>
+        <v>128276953</v>
       </c>
       <c r="B29" t="n">
-        <v>98571</v>
+        <v>92736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547999</v>
+        <v>548012</v>
       </c>
       <c r="R29" t="n">
-        <v>6960288</v>
+        <v>6960292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3703,19 +3699,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3730,22 +3716,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128276953</v>
+        <v>128274393</v>
       </c>
       <c r="B30" t="n">
-        <v>92736</v>
+        <v>79083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3753,34 +3739,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548012</v>
+        <v>547975</v>
       </c>
       <c r="R30" t="n">
-        <v>6960292</v>
+        <v>6960341</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3810,9 +3796,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3827,22 +3823,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128274393</v>
+        <v>128274501</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3850,34 +3846,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
         <v>547975</v>
       </c>
       <c r="R31" t="n">
-        <v>6960341</v>
+        <v>6960313</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3907,19 +3908,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3934,62 +3925,61 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128274501</v>
+        <v>128275283</v>
       </c>
       <c r="B32" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547975</v>
+        <v>547999</v>
       </c>
       <c r="R32" t="n">
-        <v>6960313</v>
+        <v>6960288</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4019,9 +4009,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,61 +4036,61 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128274383</v>
+        <v>128277337</v>
       </c>
       <c r="B33" t="n">
-        <v>92742</v>
+        <v>98571</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547964</v>
+        <v>547930</v>
       </c>
       <c r="R33" t="n">
-        <v>6960346</v>
+        <v>6960191</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4120,9 +4120,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4137,49 +4147,49 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128277264</v>
+        <v>128277041</v>
       </c>
       <c r="B34" t="n">
-        <v>80217</v>
+        <v>98571</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4188,10 +4198,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547947</v>
+        <v>547984</v>
       </c>
       <c r="R34" t="n">
-        <v>6960412</v>
+        <v>6960265</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4223,7 +4233,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4233,7 +4243,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4244,41 +4254,16 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4396,32 +4381,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128277041</v>
+        <v>128274383</v>
       </c>
       <c r="B36" t="n">
-        <v>98571</v>
+        <v>92742</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4431,17 +4416,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547984</v>
+        <v>547964</v>
       </c>
       <c r="R36" t="n">
-        <v>6960265</v>
+        <v>6960346</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4468,19 +4453,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4495,64 +4470,64 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128277337</v>
+        <v>128277264</v>
       </c>
       <c r="B37" t="n">
-        <v>98571</v>
+        <v>80217</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547930</v>
+        <v>547947</v>
       </c>
       <c r="R37" t="n">
-        <v>6960191</v>
+        <v>6960412</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4581,7 +4556,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4591,7 +4566,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4602,53 +4577,79 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128274698</v>
+        <v>128274387</v>
       </c>
       <c r="B38" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4657,10 +4658,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>547997</v>
+        <v>548056</v>
       </c>
       <c r="R38" t="n">
-        <v>6960315</v>
+        <v>6960360</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4692,7 +4693,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4702,7 +4703,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4717,12 +4723,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4845,38 +4851,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128274387</v>
+        <v>128274698</v>
       </c>
       <c r="B40" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4885,10 +4890,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548056</v>
+        <v>547997</v>
       </c>
       <c r="R40" t="n">
-        <v>6960360</v>
+        <v>6960315</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4920,7 +4925,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4930,12 +4935,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4950,12 +4950,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -6025,52 +6025,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128277370</v>
+        <v>128284858</v>
       </c>
       <c r="B51" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547938</v>
+        <v>547979</v>
       </c>
       <c r="R51" t="n">
-        <v>6960182</v>
+        <v>6960273</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6099,7 +6095,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6109,7 +6105,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6124,60 +6120,64 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128284858</v>
+        <v>128277370</v>
       </c>
       <c r="B52" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547979</v>
+        <v>547938</v>
       </c>
       <c r="R52" t="n">
-        <v>6960273</v>
+        <v>6960182</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6231,15 +6231,597 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128622889</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92742</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>547917</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6960175</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128622880</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79702</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>547985</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6960264</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128622885</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80189</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>548031</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6960282</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128622891</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92736</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>548038</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6960220</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128622887</v>
+      </c>
+      <c r="B57" t="n">
+        <v>81068</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>547959</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6960371</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128622888</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78840</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>547937</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6960418</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -1779,10 +1779,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128274733</v>
+        <v>128274521</v>
       </c>
       <c r="B12" t="n">
-        <v>57685</v>
+        <v>75163</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,42 +1790,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547968</v>
+        <v>547947</v>
       </c>
       <c r="R12" t="n">
-        <v>6960276</v>
+        <v>6960412</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,14 +1851,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,26 +1874,51 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128274521</v>
+        <v>128274733</v>
       </c>
       <c r="B13" t="n">
-        <v>75163</v>
+        <v>57685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,41 +1926,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547947</v>
+        <v>547968</v>
       </c>
       <c r="R13" t="n">
-        <v>6960412</v>
+        <v>6960276</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1958,19 +1988,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:26</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1981,41 +2006,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128274594</v>
+        <v>128273826</v>
       </c>
       <c r="B16" t="n">
-        <v>80188</v>
+        <v>57685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,34 +2247,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548040</v>
+        <v>547957</v>
       </c>
       <c r="R16" t="n">
-        <v>6960306</v>
+        <v>6960424</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2311,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2316,7 +2321,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,10 +2353,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128284856</v>
+        <v>128274594</v>
       </c>
       <c r="B17" t="n">
-        <v>78840</v>
+        <v>80188</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,37 +2364,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547952</v>
+        <v>548040</v>
       </c>
       <c r="R17" t="n">
-        <v>6960362</v>
+        <v>6960306</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2413,7 +2423,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2433,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2438,19 +2448,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128277304</v>
+        <v>128284856</v>
       </c>
       <c r="B18" t="n">
         <v>78840</v>
@@ -2481,17 +2491,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547936</v>
+        <v>547952</v>
       </c>
       <c r="R18" t="n">
-        <v>6960173</v>
+        <v>6960362</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2520,7 +2530,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2540,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,22 +2555,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128273826</v>
+        <v>128277304</v>
       </c>
       <c r="B19" t="n">
-        <v>57685</v>
+        <v>78840</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,39 +2578,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547957</v>
+        <v>547936</v>
       </c>
       <c r="R19" t="n">
-        <v>6960424</v>
+        <v>6960173</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2637,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,12 +2647,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2662,12 +2662,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -4048,49 +4048,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128277337</v>
+        <v>128274383</v>
       </c>
       <c r="B33" t="n">
-        <v>98571</v>
+        <v>92742</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547930</v>
+        <v>547964</v>
       </c>
       <c r="R33" t="n">
-        <v>6960191</v>
+        <v>6960346</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4120,19 +4120,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4147,49 +4137,49 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128277041</v>
+        <v>128277264</v>
       </c>
       <c r="B34" t="n">
-        <v>98571</v>
+        <v>80217</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4198,10 +4188,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547984</v>
+        <v>547947</v>
       </c>
       <c r="R34" t="n">
-        <v>6960265</v>
+        <v>6960412</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4233,7 +4223,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4243,7 +4233,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4254,16 +4244,41 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4381,32 +4396,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128274383</v>
+        <v>128277041</v>
       </c>
       <c r="B36" t="n">
-        <v>92742</v>
+        <v>98571</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4416,17 +4431,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547964</v>
+        <v>547984</v>
       </c>
       <c r="R36" t="n">
-        <v>6960346</v>
+        <v>6960265</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4453,9 +4468,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,64 +4495,64 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128277264</v>
+        <v>128277337</v>
       </c>
       <c r="B37" t="n">
-        <v>80217</v>
+        <v>98571</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547947</v>
+        <v>547930</v>
       </c>
       <c r="R37" t="n">
-        <v>6960412</v>
+        <v>6960191</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4556,7 +4581,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4566,7 +4591,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4577,41 +4602,16 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4735,7 +4735,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128278639</v>
+        <v>128274698</v>
       </c>
       <c r="B39" t="n">
         <v>98571</v>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4774,13 +4774,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>547947</v>
+        <v>547997</v>
       </c>
       <c r="R39" t="n">
-        <v>6960412</v>
+        <v>6960315</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4830,28 +4830,23 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128274698</v>
+        <v>128278639</v>
       </c>
       <c r="B40" t="n">
         <v>98571</v>
@@ -4881,7 +4876,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>36</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4890,13 +4885,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547997</v>
+        <v>547947</v>
       </c>
       <c r="R40" t="n">
-        <v>6960315</v>
+        <v>6960412</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4925,7 +4920,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4935,7 +4930,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4946,16 +4941,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5166,45 +5166,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128274466</v>
+        <v>128277134</v>
       </c>
       <c r="B43" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548066</v>
+        <v>547979</v>
       </c>
       <c r="R43" t="n">
-        <v>6960351</v>
+        <v>6960221</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5236,7 +5240,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5246,7 +5250,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5261,22 +5265,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128274083</v>
+        <v>128274466</v>
       </c>
       <c r="B44" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5284,39 +5288,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547956</v>
+        <v>548066</v>
       </c>
       <c r="R44" t="n">
-        <v>6960372</v>
+        <v>6960351</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5346,14 +5345,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5368,61 +5372,62 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128277134</v>
+        <v>128274083</v>
       </c>
       <c r="B45" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547979</v>
+        <v>547956</v>
       </c>
       <c r="R45" t="n">
-        <v>6960221</v>
+        <v>6960372</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5452,19 +5457,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:05</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5479,12 +5479,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6243,32 +6243,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128622889</v>
+        <v>128622880</v>
       </c>
       <c r="B53" t="n">
-        <v>92742</v>
+        <v>79702</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547917</v>
+        <v>547985</v>
       </c>
       <c r="R53" t="n">
-        <v>6960175</v>
+        <v>6960264</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6340,32 +6340,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128622880</v>
+        <v>128622889</v>
       </c>
       <c r="B54" t="n">
-        <v>79702</v>
+        <v>92742</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547985</v>
+        <v>547917</v>
       </c>
       <c r="R54" t="n">
-        <v>6960264</v>
+        <v>6960175</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -1779,10 +1779,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128274521</v>
+        <v>128274733</v>
       </c>
       <c r="B12" t="n">
-        <v>75163</v>
+        <v>57685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,41 +1790,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547947</v>
+        <v>547968</v>
       </c>
       <c r="R12" t="n">
-        <v>6960412</v>
+        <v>6960276</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,19 +1852,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:26</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,51 +1870,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128274733</v>
+        <v>128274521</v>
       </c>
       <c r="B13" t="n">
-        <v>57685</v>
+        <v>75163</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1926,42 +1897,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547968</v>
+        <v>547947</v>
       </c>
       <c r="R13" t="n">
-        <v>6960276</v>
+        <v>6960412</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1988,14 +1958,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,61 +1981,86 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128277341</v>
+        <v>128274594</v>
       </c>
       <c r="B14" t="n">
-        <v>92742</v>
+        <v>80188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547935</v>
+        <v>548040</v>
       </c>
       <c r="R14" t="n">
-        <v>6960188</v>
+        <v>6960306</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,48 +2129,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128277049</v>
+        <v>128284856</v>
       </c>
       <c r="B15" t="n">
-        <v>92742</v>
+        <v>78840</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547985</v>
+        <v>547952</v>
       </c>
       <c r="R15" t="n">
-        <v>6960231</v>
+        <v>6960362</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,22 +2224,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128273826</v>
+        <v>128277304</v>
       </c>
       <c r="B16" t="n">
-        <v>57685</v>
+        <v>78840</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,39 +2247,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547957</v>
+        <v>547936</v>
       </c>
       <c r="R16" t="n">
-        <v>6960424</v>
+        <v>6960173</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2321,12 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,57 +2331,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128274594</v>
+        <v>128277341</v>
       </c>
       <c r="B17" t="n">
-        <v>80188</v>
+        <v>92742</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548040</v>
+        <v>547935</v>
       </c>
       <c r="R17" t="n">
-        <v>6960306</v>
+        <v>6960188</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2423,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2433,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2460,48 +2450,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128284856</v>
+        <v>128277049</v>
       </c>
       <c r="B18" t="n">
-        <v>78840</v>
+        <v>92742</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547952</v>
+        <v>547985</v>
       </c>
       <c r="R18" t="n">
-        <v>6960362</v>
+        <v>6960231</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2530,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2540,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2555,22 +2545,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128277304</v>
+        <v>128273826</v>
       </c>
       <c r="B19" t="n">
-        <v>78840</v>
+        <v>57685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,34 +2568,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547936</v>
+        <v>547957</v>
       </c>
       <c r="R19" t="n">
-        <v>6960173</v>
+        <v>6960424</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2637,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2647,7 +2642,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2662,12 +2662,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2888,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128277198</v>
+        <v>128274886</v>
       </c>
       <c r="B22" t="n">
-        <v>57685</v>
+        <v>80189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,39 +2899,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547970</v>
+        <v>548022</v>
       </c>
       <c r="R22" t="n">
-        <v>6960207</v>
+        <v>6960304</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2961,14 +2956,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2983,22 +2983,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128274886</v>
+        <v>128277198</v>
       </c>
       <c r="B23" t="n">
-        <v>80189</v>
+        <v>57685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,34 +3006,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548022</v>
+        <v>547970</v>
       </c>
       <c r="R23" t="n">
-        <v>6960304</v>
+        <v>6960207</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3063,19 +3068,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:46</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,12 +3090,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4048,52 +4048,52 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128274383</v>
+        <v>128274414</v>
       </c>
       <c r="B33" t="n">
-        <v>92742</v>
+        <v>98571</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547964</v>
+        <v>547966</v>
       </c>
       <c r="R33" t="n">
-        <v>6960346</v>
+        <v>6960356</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4120,9 +4120,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4137,49 +4147,49 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128277264</v>
+        <v>128277041</v>
       </c>
       <c r="B34" t="n">
-        <v>80217</v>
+        <v>98571</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4188,10 +4198,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547947</v>
+        <v>547984</v>
       </c>
       <c r="R34" t="n">
-        <v>6960412</v>
+        <v>6960265</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4223,7 +4233,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4233,7 +4243,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4244,48 +4254,23 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128274414</v>
+        <v>128277337</v>
       </c>
       <c r="B35" t="n">
         <v>98571</v>
@@ -4315,22 +4300,22 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547966</v>
+        <v>547930</v>
       </c>
       <c r="R35" t="n">
-        <v>6960356</v>
+        <v>6960191</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4359,7 +4344,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4369,7 +4354,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4384,44 +4369,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128277041</v>
+        <v>128274383</v>
       </c>
       <c r="B36" t="n">
-        <v>98571</v>
+        <v>92742</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4431,17 +4416,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547984</v>
+        <v>547964</v>
       </c>
       <c r="R36" t="n">
-        <v>6960265</v>
+        <v>6960346</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4468,19 +4453,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4495,64 +4470,64 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128277337</v>
+        <v>128277264</v>
       </c>
       <c r="B37" t="n">
-        <v>98571</v>
+        <v>80217</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547930</v>
+        <v>547947</v>
       </c>
       <c r="R37" t="n">
-        <v>6960191</v>
+        <v>6960412</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4581,7 +4556,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4591,7 +4566,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4602,16 +4577,41 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5166,49 +5166,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128277134</v>
+        <v>128274083</v>
       </c>
       <c r="B43" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547979</v>
+        <v>547956</v>
       </c>
       <c r="R43" t="n">
-        <v>6960221</v>
+        <v>6960372</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5238,19 +5239,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:05</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5265,12 +5261,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5384,50 +5380,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128274083</v>
+        <v>128277134</v>
       </c>
       <c r="B45" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547956</v>
+        <v>547979</v>
       </c>
       <c r="R45" t="n">
-        <v>6960372</v>
+        <v>6960221</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5457,14 +5452,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5479,12 +5479,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5593,37 +5593,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128274007</v>
+        <v>128276966</v>
       </c>
       <c r="B47" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5632,10 +5633,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547955</v>
+        <v>548010</v>
       </c>
       <c r="R47" t="n">
-        <v>6960412</v>
+        <v>6960276</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5667,7 +5668,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5677,7 +5678,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5692,50 +5698,49 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128276966</v>
+        <v>128274007</v>
       </c>
       <c r="B48" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5744,10 +5749,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548010</v>
+        <v>547955</v>
       </c>
       <c r="R48" t="n">
-        <v>6960276</v>
+        <v>6960412</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5779,7 +5784,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5789,12 +5794,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5809,12 +5809,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6246,7 +6246,7 @@
         <v>128622880</v>
       </c>
       <c r="B53" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>128622889</v>
       </c>
       <c r="B54" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>128622885</v>
       </c>
       <c r="B55" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>128622891</v>
       </c>
       <c r="B56" t="n">
-        <v>92736</v>
+        <v>92742</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128622887</v>
       </c>
       <c r="B57" t="n">
-        <v>81068</v>
+        <v>81072</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128622888</v>
       </c>
       <c r="B58" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -1364,7 +1364,7 @@
         <v>128277319</v>
       </c>
       <c r="B8" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>128277379</v>
       </c>
       <c r="B9" t="n">
-        <v>98605</v>
+        <v>98619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,48 +1575,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128284855</v>
+        <v>128274290</v>
       </c>
       <c r="B10" t="n">
-        <v>80188</v>
+        <v>96708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547938</v>
+        <v>547959</v>
       </c>
       <c r="R10" t="n">
-        <v>6960421</v>
+        <v>6960358</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1643,19 +1643,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,60 +1660,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128274290</v>
+        <v>128284855</v>
       </c>
       <c r="B11" t="n">
-        <v>96696</v>
+        <v>80192</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547959</v>
+        <v>547938</v>
       </c>
       <c r="R11" t="n">
-        <v>6960358</v>
+        <v>6960421</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1750,9 +1740,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,12 +1767,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1782,7 +1782,7 @@
         <v>128274733</v>
       </c>
       <c r="B12" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>128274521</v>
       </c>
       <c r="B13" t="n">
-        <v>75163</v>
+        <v>75167</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,32 +2022,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128274594</v>
+        <v>128277049</v>
       </c>
       <c r="B14" t="n">
-        <v>80188</v>
+        <v>92754</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548040</v>
+        <v>547985</v>
       </c>
       <c r="R14" t="n">
-        <v>6960306</v>
+        <v>6960231</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,60 +2117,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128284856</v>
+        <v>128277341</v>
       </c>
       <c r="B15" t="n">
-        <v>78840</v>
+        <v>92754</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547952</v>
+        <v>547935</v>
       </c>
       <c r="R15" t="n">
-        <v>6960362</v>
+        <v>6960188</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,22 +2224,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128277304</v>
+        <v>128284856</v>
       </c>
       <c r="B16" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,17 +2267,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547936</v>
+        <v>547952</v>
       </c>
       <c r="R16" t="n">
-        <v>6960173</v>
+        <v>6960362</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2331,44 +2331,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128277341</v>
+        <v>128277304</v>
       </c>
       <c r="B17" t="n">
-        <v>92742</v>
+        <v>78844</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547935</v>
+        <v>547936</v>
       </c>
       <c r="R17" t="n">
-        <v>6960188</v>
+        <v>6960173</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2438,44 +2438,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128277049</v>
+        <v>128274594</v>
       </c>
       <c r="B18" t="n">
-        <v>92742</v>
+        <v>80192</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547985</v>
+        <v>548040</v>
       </c>
       <c r="R18" t="n">
-        <v>6960231</v>
+        <v>6960306</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,12 +2545,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2560,7 +2560,7 @@
         <v>128273826</v>
       </c>
       <c r="B19" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>128277456</v>
       </c>
       <c r="B20" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>128274743</v>
       </c>
       <c r="B21" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>128274886</v>
       </c>
       <c r="B22" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>128277198</v>
       </c>
       <c r="B23" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>128284854</v>
       </c>
       <c r="B24" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3209,38 +3209,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128273858</v>
+        <v>128275378</v>
       </c>
       <c r="B25" t="n">
-        <v>57685</v>
+        <v>98585</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3249,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547952</v>
+        <v>548012</v>
       </c>
       <c r="R25" t="n">
-        <v>6960420</v>
+        <v>6960292</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3285,11 +3284,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3316,37 +3310,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128275378</v>
+        <v>128273858</v>
       </c>
       <c r="B26" t="n">
-        <v>98571</v>
+        <v>57689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3355,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548012</v>
+        <v>547952</v>
       </c>
       <c r="R26" t="n">
-        <v>6960292</v>
+        <v>6960420</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3391,6 +3386,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3420,7 +3420,7 @@
         <v>128278609</v>
       </c>
       <c r="B27" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128273941</v>
       </c>
       <c r="B28" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3631,10 +3631,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128276953</v>
+        <v>128274393</v>
       </c>
       <c r="B29" t="n">
-        <v>92736</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3642,34 +3642,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548012</v>
+        <v>547975</v>
       </c>
       <c r="R29" t="n">
-        <v>6960292</v>
+        <v>6960341</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3699,9 +3699,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3716,22 +3726,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128274393</v>
+        <v>128274501</v>
       </c>
       <c r="B30" t="n">
-        <v>79083</v>
+        <v>57689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3739,34 +3749,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
         <v>547975</v>
       </c>
       <c r="R30" t="n">
-        <v>6960341</v>
+        <v>6960313</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3796,19 +3811,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3823,22 +3828,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128274501</v>
+        <v>128276953</v>
       </c>
       <c r="B31" t="n">
-        <v>57685</v>
+        <v>92748</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3846,39 +3851,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>547975</v>
+        <v>548012</v>
       </c>
       <c r="R31" t="n">
-        <v>6960313</v>
+        <v>6960292</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,7 +3940,7 @@
         <v>128275283</v>
       </c>
       <c r="B32" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>128274414</v>
       </c>
       <c r="B33" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>128277041</v>
       </c>
       <c r="B34" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>128277337</v>
       </c>
       <c r="B35" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>128274383</v>
       </c>
       <c r="B36" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>128277264</v>
       </c>
       <c r="B37" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>128274387</v>
       </c>
       <c r="B38" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>128274698</v>
       </c>
       <c r="B39" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>128278639</v>
       </c>
       <c r="B40" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>128274742</v>
       </c>
       <c r="B41" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>128273967</v>
       </c>
       <c r="B42" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128274083</v>
+        <v>128274466</v>
       </c>
       <c r="B43" t="n">
-        <v>57685</v>
+        <v>80192</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5177,39 +5177,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547956</v>
+        <v>548066</v>
       </c>
       <c r="R43" t="n">
-        <v>6960372</v>
+        <v>6960351</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5239,14 +5234,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5261,22 +5261,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128274466</v>
+        <v>128274083</v>
       </c>
       <c r="B44" t="n">
-        <v>80188</v>
+        <v>57689</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5284,34 +5284,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548066</v>
+        <v>547956</v>
       </c>
       <c r="R44" t="n">
-        <v>6960351</v>
+        <v>6960372</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5341,19 +5346,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:23</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5368,12 +5368,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5383,7 +5383,7 @@
         <v>128277134</v>
       </c>
       <c r="B45" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>128277422</v>
       </c>
       <c r="B46" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,38 +5593,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128276966</v>
+        <v>128274007</v>
       </c>
       <c r="B47" t="n">
-        <v>57685</v>
+        <v>98585</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5633,10 +5632,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548010</v>
+        <v>547955</v>
       </c>
       <c r="R47" t="n">
-        <v>6960276</v>
+        <v>6960412</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5668,7 +5667,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5678,12 +5677,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5698,49 +5692,50 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128274007</v>
+        <v>128276966</v>
       </c>
       <c r="B48" t="n">
-        <v>98571</v>
+        <v>57689</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5749,10 +5744,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547955</v>
+        <v>548010</v>
       </c>
       <c r="R48" t="n">
-        <v>6960412</v>
+        <v>6960276</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5784,7 +5779,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5794,7 +5789,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5809,12 +5809,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5824,7 +5824,7 @@
         <v>128277116</v>
       </c>
       <c r="B49" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128274041</v>
       </c>
       <c r="B50" t="n">
-        <v>80216</v>
+        <v>80220</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>128284858</v>
       </c>
       <c r="B51" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>128277370</v>
       </c>
       <c r="B52" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>128622889</v>
       </c>
       <c r="B54" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>128622891</v>
       </c>
       <c r="B56" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>128277379</v>
       </c>
       <c r="B9" t="n">
-        <v>98619</v>
+        <v>98622</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>128274290</v>
       </c>
       <c r="B10" t="n">
-        <v>96708</v>
+        <v>96710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>128284855</v>
       </c>
       <c r="B11" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128274733</v>
+        <v>128274521</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>75169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,42 +1790,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547968</v>
+        <v>547947</v>
       </c>
       <c r="R12" t="n">
-        <v>6960276</v>
+        <v>6960412</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,14 +1851,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,26 +1874,51 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128274521</v>
+        <v>128274733</v>
       </c>
       <c r="B13" t="n">
-        <v>75167</v>
+        <v>57689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,41 +1926,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547947</v>
+        <v>547968</v>
       </c>
       <c r="R13" t="n">
-        <v>6960412</v>
+        <v>6960276</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1958,19 +1988,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:26</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1981,41 +2006,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2025,7 +2025,7 @@
         <v>128277049</v>
       </c>
       <c r="B14" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>128277341</v>
       </c>
       <c r="B15" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128284856</v>
+        <v>128277304</v>
       </c>
       <c r="B16" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,17 +2267,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547952</v>
+        <v>547936</v>
       </c>
       <c r="R16" t="n">
-        <v>6960362</v>
+        <v>6960173</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2331,22 +2331,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128277304</v>
+        <v>128284856</v>
       </c>
       <c r="B17" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,17 +2374,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547936</v>
+        <v>547952</v>
       </c>
       <c r="R17" t="n">
-        <v>6960173</v>
+        <v>6960362</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2438,12 +2438,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2453,7 +2453,7 @@
         <v>128274594</v>
       </c>
       <c r="B18" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>128277456</v>
       </c>
       <c r="B20" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>128274743</v>
       </c>
       <c r="B21" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128274886</v>
+        <v>128284854</v>
       </c>
       <c r="B22" t="n">
-        <v>80193</v>
+        <v>78847</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,37 +2899,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548022</v>
+        <v>547936</v>
       </c>
       <c r="R22" t="n">
-        <v>6960304</v>
+        <v>6960436</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2983,22 +2983,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128277198</v>
+        <v>128274886</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>80195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,39 +3006,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547970</v>
+        <v>548022</v>
       </c>
       <c r="R23" t="n">
-        <v>6960207</v>
+        <v>6960304</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3068,14 +3063,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,22 +3090,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128284854</v>
+        <v>128277198</v>
       </c>
       <c r="B24" t="n">
-        <v>78845</v>
+        <v>57689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,37 +3113,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547936</v>
+        <v>547970</v>
       </c>
       <c r="R24" t="n">
-        <v>6960436</v>
+        <v>6960207</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3170,19 +3175,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:56</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3197,12 +3197,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3212,7 +3212,7 @@
         <v>128275378</v>
       </c>
       <c r="B25" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>128278609</v>
       </c>
       <c r="B27" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128273941</v>
       </c>
       <c r="B28" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3631,10 +3631,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128274393</v>
+        <v>128276953</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>92750</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3642,34 +3642,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547975</v>
+        <v>548012</v>
       </c>
       <c r="R29" t="n">
-        <v>6960341</v>
+        <v>6960292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3699,19 +3699,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3726,22 +3716,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128274501</v>
+        <v>128274393</v>
       </c>
       <c r="B30" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,39 +3739,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
         <v>547975</v>
       </c>
       <c r="R30" t="n">
-        <v>6960313</v>
+        <v>6960341</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3811,9 +3796,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3828,22 +3823,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128276953</v>
+        <v>128274501</v>
       </c>
       <c r="B31" t="n">
-        <v>92748</v>
+        <v>57689</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3851,34 +3846,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548012</v>
+        <v>547975</v>
       </c>
       <c r="R31" t="n">
-        <v>6960292</v>
+        <v>6960313</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,7 +3940,7 @@
         <v>128275283</v>
       </c>
       <c r="B32" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4048,52 +4048,52 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128274414</v>
+        <v>128274383</v>
       </c>
       <c r="B33" t="n">
-        <v>98585</v>
+        <v>92756</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547966</v>
+        <v>547964</v>
       </c>
       <c r="R33" t="n">
-        <v>6960356</v>
+        <v>6960346</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4120,19 +4120,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4147,49 +4137,49 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128277041</v>
+        <v>128277264</v>
       </c>
       <c r="B34" t="n">
-        <v>98585</v>
+        <v>80223</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4198,10 +4188,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547984</v>
+        <v>547947</v>
       </c>
       <c r="R34" t="n">
-        <v>6960265</v>
+        <v>6960412</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4233,7 +4223,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4243,7 +4233,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4254,16 +4244,41 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4273,7 +4288,7 @@
         <v>128277337</v>
       </c>
       <c r="B35" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,32 +4396,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128274383</v>
+        <v>128277041</v>
       </c>
       <c r="B36" t="n">
-        <v>92754</v>
+        <v>98588</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4416,17 +4431,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547964</v>
+        <v>547984</v>
       </c>
       <c r="R36" t="n">
-        <v>6960346</v>
+        <v>6960265</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4453,9 +4468,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,49 +4495,49 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128277264</v>
+        <v>128274414</v>
       </c>
       <c r="B37" t="n">
-        <v>80221</v>
+        <v>98588</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4521,10 +4546,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547947</v>
+        <v>547966</v>
       </c>
       <c r="R37" t="n">
-        <v>6960412</v>
+        <v>6960356</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4556,7 +4581,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4566,7 +4591,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4577,41 +4602,16 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128274698</v>
+        <v>128278639</v>
       </c>
       <c r="B39" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>36</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4774,13 +4774,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>547997</v>
+        <v>547947</v>
       </c>
       <c r="R39" t="n">
-        <v>6960315</v>
+        <v>6960412</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4830,26 +4830,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128278639</v>
+        <v>128274698</v>
       </c>
       <c r="B40" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4876,7 +4881,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4885,13 +4890,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547947</v>
+        <v>547997</v>
       </c>
       <c r="R40" t="n">
-        <v>6960412</v>
+        <v>6960315</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4920,7 +4925,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4930,7 +4935,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4941,21 +4946,16 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4965,7 +4965,7 @@
         <v>128274742</v>
       </c>
       <c r="B41" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>128273967</v>
       </c>
       <c r="B42" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128274466</v>
+        <v>128274083</v>
       </c>
       <c r="B43" t="n">
-        <v>80192</v>
+        <v>57689</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5177,34 +5177,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548066</v>
+        <v>547956</v>
       </c>
       <c r="R43" t="n">
-        <v>6960351</v>
+        <v>6960372</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5234,19 +5239,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:23</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5261,22 +5261,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128274083</v>
+        <v>128274466</v>
       </c>
       <c r="B44" t="n">
-        <v>57689</v>
+        <v>80194</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5284,39 +5284,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547956</v>
+        <v>548066</v>
       </c>
       <c r="R44" t="n">
-        <v>6960372</v>
+        <v>6960351</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5346,14 +5341,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5368,12 +5368,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5383,7 +5383,7 @@
         <v>128277134</v>
       </c>
       <c r="B45" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5593,37 +5593,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128274007</v>
+        <v>128276966</v>
       </c>
       <c r="B47" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5632,10 +5633,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547955</v>
+        <v>548010</v>
       </c>
       <c r="R47" t="n">
-        <v>6960412</v>
+        <v>6960276</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5667,7 +5668,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5677,7 +5678,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5692,50 +5698,49 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128276966</v>
+        <v>128274007</v>
       </c>
       <c r="B48" t="n">
-        <v>57689</v>
+        <v>98588</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5744,10 +5749,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548010</v>
+        <v>547955</v>
       </c>
       <c r="R48" t="n">
-        <v>6960276</v>
+        <v>6960412</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5779,7 +5784,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5789,12 +5794,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5809,12 +5809,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5824,7 +5824,7 @@
         <v>128277116</v>
       </c>
       <c r="B49" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128274041</v>
       </c>
       <c r="B50" t="n">
-        <v>80220</v>
+        <v>80222</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6025,48 +6025,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128284858</v>
+        <v>128277370</v>
       </c>
       <c r="B51" t="n">
-        <v>80192</v>
+        <v>98588</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547979</v>
+        <v>547938</v>
       </c>
       <c r="R51" t="n">
-        <v>6960273</v>
+        <v>6960182</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6095,7 +6099,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6105,7 +6109,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6120,64 +6124,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128277370</v>
+        <v>128284858</v>
       </c>
       <c r="B52" t="n">
-        <v>98585</v>
+        <v>80194</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547938</v>
+        <v>547979</v>
       </c>
       <c r="R52" t="n">
-        <v>6960182</v>
+        <v>6960273</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6231,12 +6231,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6246,7 +6246,7 @@
         <v>128622880</v>
       </c>
       <c r="B53" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>128622889</v>
       </c>
       <c r="B54" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>128622885</v>
       </c>
       <c r="B55" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>128622891</v>
       </c>
       <c r="B56" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128622887</v>
       </c>
       <c r="B57" t="n">
-        <v>81072</v>
+        <v>81074</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128622888</v>
       </c>
       <c r="B58" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>128277379</v>
       </c>
       <c r="B9" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128274521</v>
+        <v>128274733</v>
       </c>
       <c r="B12" t="n">
-        <v>75169</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,41 +1790,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547947</v>
+        <v>547968</v>
       </c>
       <c r="R12" t="n">
-        <v>6960412</v>
+        <v>6960276</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,19 +1852,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:26</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,51 +1870,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128274733</v>
+        <v>128274521</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>75169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1926,42 +1897,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547968</v>
+        <v>547947</v>
       </c>
       <c r="R13" t="n">
-        <v>6960276</v>
+        <v>6960412</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1988,14 +1958,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,48 +1981,73 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128277049</v>
+        <v>128274594</v>
       </c>
       <c r="B14" t="n">
-        <v>92756</v>
+        <v>80194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547985</v>
+        <v>548040</v>
       </c>
       <c r="R14" t="n">
-        <v>6960231</v>
+        <v>6960306</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,60 +2117,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128277341</v>
+        <v>128284856</v>
       </c>
       <c r="B15" t="n">
-        <v>92756</v>
+        <v>78846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547935</v>
+        <v>547952</v>
       </c>
       <c r="R15" t="n">
-        <v>6960188</v>
+        <v>6960362</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,12 +2224,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2343,48 +2343,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128284856</v>
+        <v>128277341</v>
       </c>
       <c r="B17" t="n">
-        <v>78846</v>
+        <v>92756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547952</v>
+        <v>547935</v>
       </c>
       <c r="R17" t="n">
-        <v>6960362</v>
+        <v>6960188</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2438,44 +2438,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128274594</v>
+        <v>128277049</v>
       </c>
       <c r="B18" t="n">
-        <v>80194</v>
+        <v>92756</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548040</v>
+        <v>547985</v>
       </c>
       <c r="R18" t="n">
-        <v>6960306</v>
+        <v>6960231</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,12 +2545,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2674,45 +2674,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128277456</v>
+        <v>128274743</v>
       </c>
       <c r="B20" t="n">
-        <v>92756</v>
+        <v>80194</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547921</v>
+        <v>548016</v>
       </c>
       <c r="R20" t="n">
-        <v>6960179</v>
+        <v>6960300</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2769,57 +2769,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128274743</v>
+        <v>128277456</v>
       </c>
       <c r="B21" t="n">
-        <v>80194</v>
+        <v>92756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548016</v>
+        <v>547921</v>
       </c>
       <c r="R21" t="n">
-        <v>6960300</v>
+        <v>6960179</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2876,22 +2876,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128284854</v>
+        <v>128274886</v>
       </c>
       <c r="B22" t="n">
-        <v>78847</v>
+        <v>80195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,37 +2899,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547936</v>
+        <v>548022</v>
       </c>
       <c r="R22" t="n">
-        <v>6960436</v>
+        <v>6960304</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2983,22 +2983,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128274886</v>
+        <v>128284854</v>
       </c>
       <c r="B23" t="n">
-        <v>80195</v>
+        <v>78847</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,37 +3006,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548022</v>
+        <v>547936</v>
       </c>
       <c r="R23" t="n">
-        <v>6960304</v>
+        <v>6960436</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,12 +3090,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3209,37 +3209,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128275378</v>
+        <v>128273858</v>
       </c>
       <c r="B25" t="n">
-        <v>98588</v>
+        <v>57689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3248,10 +3249,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548012</v>
+        <v>547952</v>
       </c>
       <c r="R25" t="n">
-        <v>6960292</v>
+        <v>6960420</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3284,6 +3285,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3310,38 +3316,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128273858</v>
+        <v>128275378</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3350,10 +3355,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547952</v>
+        <v>548012</v>
       </c>
       <c r="R26" t="n">
-        <v>6960420</v>
+        <v>6960292</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3386,11 +3391,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3631,10 +3631,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128276953</v>
+        <v>128274501</v>
       </c>
       <c r="B29" t="n">
-        <v>92750</v>
+        <v>57689</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3642,34 +3642,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548012</v>
+        <v>547975</v>
       </c>
       <c r="R29" t="n">
-        <v>6960292</v>
+        <v>6960313</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3728,45 +3733,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128274393</v>
+        <v>128275283</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>98591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547975</v>
+        <v>547999</v>
       </c>
       <c r="R30" t="n">
-        <v>6960341</v>
+        <v>6960288</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,7 +3807,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3808,7 +3817,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3835,10 +3844,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128274501</v>
+        <v>128276953</v>
       </c>
       <c r="B31" t="n">
-        <v>57689</v>
+        <v>92750</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3846,39 +3855,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>547975</v>
+        <v>548012</v>
       </c>
       <c r="R31" t="n">
-        <v>6960313</v>
+        <v>6960292</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3937,49 +3941,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128275283</v>
+        <v>128274393</v>
       </c>
       <c r="B32" t="n">
-        <v>98588</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547999</v>
+        <v>547975</v>
       </c>
       <c r="R32" t="n">
-        <v>6960288</v>
+        <v>6960341</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4048,10 +4048,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128274383</v>
+        <v>128277264</v>
       </c>
       <c r="B33" t="n">
-        <v>92756</v>
+        <v>80223</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4059,41 +4059,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547964</v>
+        <v>547947</v>
       </c>
       <c r="R33" t="n">
-        <v>6960346</v>
+        <v>6960412</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4120,11 +4120,21 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4133,68 +4143,93 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128277264</v>
+        <v>128277337</v>
       </c>
       <c r="B34" t="n">
-        <v>80223</v>
+        <v>98591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547947</v>
+        <v>547930</v>
       </c>
       <c r="R34" t="n">
-        <v>6960412</v>
+        <v>6960191</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4223,7 +4258,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4233,7 +4268,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4244,51 +4279,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128277337</v>
+        <v>128277041</v>
       </c>
       <c r="B35" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4315,22 +4325,22 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547930</v>
+        <v>547984</v>
       </c>
       <c r="R35" t="n">
-        <v>6960191</v>
+        <v>6960265</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4359,7 +4369,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4369,7 +4379,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4384,22 +4394,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128277041</v>
+        <v>128274414</v>
       </c>
       <c r="B36" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4426,7 +4436,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4435,10 +4445,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547984</v>
+        <v>547966</v>
       </c>
       <c r="R36" t="n">
-        <v>6960265</v>
+        <v>6960356</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4470,7 +4480,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4480,7 +4490,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4507,52 +4517,52 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128274414</v>
+        <v>128274383</v>
       </c>
       <c r="B37" t="n">
-        <v>98588</v>
+        <v>92756</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547966</v>
+        <v>547964</v>
       </c>
       <c r="R37" t="n">
-        <v>6960356</v>
+        <v>6960346</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4579,19 +4589,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4606,12 +4606,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4738,7 +4738,7 @@
         <v>128278639</v>
       </c>
       <c r="B39" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>128274698</v>
       </c>
       <c r="B40" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128274083</v>
+        <v>128274466</v>
       </c>
       <c r="B43" t="n">
-        <v>57689</v>
+        <v>80194</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5177,39 +5177,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547956</v>
+        <v>548066</v>
       </c>
       <c r="R43" t="n">
-        <v>6960372</v>
+        <v>6960351</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5239,14 +5234,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5261,57 +5261,61 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128274466</v>
+        <v>128277134</v>
       </c>
       <c r="B44" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548066</v>
+        <v>547979</v>
       </c>
       <c r="R44" t="n">
-        <v>6960351</v>
+        <v>6960221</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5343,7 +5347,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5353,7 +5357,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5368,61 +5372,62 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128277134</v>
+        <v>128274083</v>
       </c>
       <c r="B45" t="n">
-        <v>98588</v>
+        <v>57689</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547979</v>
+        <v>547956</v>
       </c>
       <c r="R45" t="n">
-        <v>6960221</v>
+        <v>6960372</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5452,19 +5457,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:05</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5479,12 +5479,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5713,7 +5713,7 @@
         <v>128274007</v>
       </c>
       <c r="B48" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6025,52 +6025,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128277370</v>
+        <v>128284858</v>
       </c>
       <c r="B51" t="n">
-        <v>98588</v>
+        <v>80194</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547938</v>
+        <v>547979</v>
       </c>
       <c r="R51" t="n">
-        <v>6960182</v>
+        <v>6960273</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6099,7 +6095,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6109,7 +6105,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6124,60 +6120,64 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128284858</v>
+        <v>128277370</v>
       </c>
       <c r="B52" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547979</v>
+        <v>547938</v>
       </c>
       <c r="R52" t="n">
-        <v>6960273</v>
+        <v>6960182</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6231,12 +6231,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -3631,10 +3631,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128274501</v>
+        <v>128274393</v>
       </c>
       <c r="B29" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3642,39 +3642,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
         <v>547975</v>
       </c>
       <c r="R29" t="n">
-        <v>6960313</v>
+        <v>6960341</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3704,9 +3699,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3721,61 +3726,62 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128275283</v>
+        <v>128274501</v>
       </c>
       <c r="B30" t="n">
-        <v>98591</v>
+        <v>57689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547999</v>
+        <v>547975</v>
       </c>
       <c r="R30" t="n">
-        <v>6960288</v>
+        <v>6960313</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3805,19 +3811,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3832,12 +3828,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3941,45 +3937,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128274393</v>
+        <v>128275283</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>98591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547975</v>
+        <v>547999</v>
       </c>
       <c r="R32" t="n">
-        <v>6960341</v>
+        <v>6960288</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>128277379</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>128274290</v>
       </c>
       <c r="B10" t="n">
-        <v>96710</v>
+        <v>96711</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128274733</v>
+        <v>128274521</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>75169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,42 +1790,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547968</v>
+        <v>547947</v>
       </c>
       <c r="R12" t="n">
-        <v>6960276</v>
+        <v>6960412</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,14 +1851,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,26 +1874,51 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128274521</v>
+        <v>128274733</v>
       </c>
       <c r="B13" t="n">
-        <v>75169</v>
+        <v>57689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,41 +1926,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547947</v>
+        <v>547968</v>
       </c>
       <c r="R13" t="n">
-        <v>6960412</v>
+        <v>6960276</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1958,19 +1988,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:26</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1981,41 +2006,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2346,7 +2346,7 @@
         <v>128277341</v>
       </c>
       <c r="B17" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128277049</v>
       </c>
       <c r="B18" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>128277456</v>
       </c>
       <c r="B21" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128284854</v>
+        <v>128277198</v>
       </c>
       <c r="B23" t="n">
-        <v>78847</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,37 +3006,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547936</v>
+        <v>547970</v>
       </c>
       <c r="R23" t="n">
-        <v>6960436</v>
+        <v>6960207</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3063,19 +3068,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:56</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,22 +3090,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128277198</v>
+        <v>128284854</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>78847</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,42 +3113,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547970</v>
+        <v>547936</v>
       </c>
       <c r="R24" t="n">
-        <v>6960207</v>
+        <v>6960436</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3175,14 +3170,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3197,12 +3197,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3319,7 +3319,7 @@
         <v>128275378</v>
       </c>
       <c r="B26" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128273941</v>
       </c>
       <c r="B28" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3631,45 +3631,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128274393</v>
+        <v>128275283</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>98592</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547975</v>
+        <v>547999</v>
       </c>
       <c r="R29" t="n">
-        <v>6960341</v>
+        <v>6960288</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3705,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3715,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,10 +3742,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128274501</v>
+        <v>128274393</v>
       </c>
       <c r="B30" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,39 +3753,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
         <v>547975</v>
       </c>
       <c r="R30" t="n">
-        <v>6960313</v>
+        <v>6960341</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3811,9 +3810,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3828,12 +3837,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3843,7 +3852,7 @@
         <v>128276953</v>
       </c>
       <c r="B31" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3937,49 +3946,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128275283</v>
+        <v>128274501</v>
       </c>
       <c r="B32" t="n">
-        <v>98591</v>
+        <v>57689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547999</v>
+        <v>547975</v>
       </c>
       <c r="R32" t="n">
-        <v>6960288</v>
+        <v>6960313</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4009,19 +4019,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,64 +4036,64 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128277264</v>
+        <v>128277337</v>
       </c>
       <c r="B33" t="n">
-        <v>80223</v>
+        <v>98592</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547947</v>
+        <v>547930</v>
       </c>
       <c r="R33" t="n">
-        <v>6960412</v>
+        <v>6960191</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4143,51 +4143,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128277337</v>
+        <v>128277041</v>
       </c>
       <c r="B34" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4214,22 +4189,22 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547930</v>
+        <v>547984</v>
       </c>
       <c r="R34" t="n">
-        <v>6960191</v>
+        <v>6960265</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4258,7 +4233,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4268,7 +4243,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4283,22 +4258,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128277041</v>
+        <v>128274414</v>
       </c>
       <c r="B35" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4325,7 +4300,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4334,10 +4309,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547984</v>
+        <v>547966</v>
       </c>
       <c r="R35" t="n">
-        <v>6960265</v>
+        <v>6960356</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4369,7 +4344,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4379,7 +4354,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4406,37 +4381,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128274414</v>
+        <v>128277264</v>
       </c>
       <c r="B36" t="n">
-        <v>98591</v>
+        <v>80223</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4445,10 +4420,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547966</v>
+        <v>547947</v>
       </c>
       <c r="R36" t="n">
-        <v>6960356</v>
+        <v>6960412</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4480,7 +4455,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4490,7 +4465,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4501,16 +4476,41 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4520,7 +4520,7 @@
         <v>128274383</v>
       </c>
       <c r="B37" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>128278639</v>
       </c>
       <c r="B39" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>128274698</v>
       </c>
       <c r="B40" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5069,45 +5069,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128273967</v>
+        <v>128277134</v>
       </c>
       <c r="B42" t="n">
-        <v>80194</v>
+        <v>98592</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>547969</v>
+        <v>547979</v>
       </c>
       <c r="R42" t="n">
-        <v>6960411</v>
+        <v>6960221</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5137,9 +5141,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5154,19 +5168,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128274466</v>
+        <v>128273967</v>
       </c>
       <c r="B43" t="n">
         <v>80194</v>
@@ -5197,14 +5211,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548066</v>
+        <v>547969</v>
       </c>
       <c r="R43" t="n">
-        <v>6960351</v>
+        <v>6960411</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5234,19 +5248,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5261,61 +5265,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128277134</v>
+        <v>128274466</v>
       </c>
       <c r="B44" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547979</v>
+        <v>548066</v>
       </c>
       <c r="R44" t="n">
-        <v>6960221</v>
+        <v>6960351</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5372,12 +5372,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5713,7 +5713,7 @@
         <v>128274007</v>
       </c>
       <c r="B48" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6025,48 +6025,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128284858</v>
+        <v>128277370</v>
       </c>
       <c r="B51" t="n">
-        <v>80194</v>
+        <v>98592</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547979</v>
+        <v>547938</v>
       </c>
       <c r="R51" t="n">
-        <v>6960273</v>
+        <v>6960182</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6095,7 +6099,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6105,7 +6109,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6120,64 +6124,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128277370</v>
+        <v>128284858</v>
       </c>
       <c r="B52" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547938</v>
+        <v>547979</v>
       </c>
       <c r="R52" t="n">
-        <v>6960182</v>
+        <v>6960273</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6231,12 +6231,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6343,7 +6343,7 @@
         <v>128622889</v>
       </c>
       <c r="B54" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>128622891</v>
       </c>
       <c r="B56" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -3209,38 +3209,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128273858</v>
+        <v>128275378</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>98592</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3249,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547952</v>
+        <v>548012</v>
       </c>
       <c r="R25" t="n">
-        <v>6960420</v>
+        <v>6960292</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3285,11 +3284,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3316,37 +3310,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128275378</v>
+        <v>128273858</v>
       </c>
       <c r="B26" t="n">
-        <v>98592</v>
+        <v>57689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3355,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548012</v>
+        <v>547952</v>
       </c>
       <c r="R26" t="n">
-        <v>6960292</v>
+        <v>6960420</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3391,6 +3386,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -6246,7 +6246,7 @@
         <v>128622880</v>
       </c>
       <c r="B53" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>128622889</v>
       </c>
       <c r="B54" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>128622885</v>
       </c>
       <c r="B55" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>128622891</v>
       </c>
       <c r="B56" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128622887</v>
       </c>
       <c r="B57" t="n">
-        <v>81074</v>
+        <v>81101</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128622888</v>
       </c>
       <c r="B58" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -1364,7 +1364,7 @@
         <v>128277319</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>128277379</v>
       </c>
       <c r="B9" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>128274290</v>
       </c>
       <c r="B10" t="n">
-        <v>96711</v>
+        <v>96738</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>128284855</v>
       </c>
       <c r="B11" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>128274521</v>
       </c>
       <c r="B12" t="n">
-        <v>75169</v>
+        <v>75196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>128274733</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,32 +2022,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128274594</v>
+        <v>128277049</v>
       </c>
       <c r="B14" t="n">
-        <v>80194</v>
+        <v>92784</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548040</v>
+        <v>547985</v>
       </c>
       <c r="R14" t="n">
-        <v>6960306</v>
+        <v>6960231</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,60 +2117,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128284856</v>
+        <v>128277341</v>
       </c>
       <c r="B15" t="n">
-        <v>78846</v>
+        <v>92784</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547952</v>
+        <v>547935</v>
       </c>
       <c r="R15" t="n">
-        <v>6960362</v>
+        <v>6960188</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,22 +2224,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128277304</v>
+        <v>128273826</v>
       </c>
       <c r="B16" t="n">
-        <v>78846</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,34 +2247,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547936</v>
+        <v>547957</v>
       </c>
       <c r="R16" t="n">
-        <v>6960173</v>
+        <v>6960424</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2311,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2316,7 +2321,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2331,60 +2341,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128277341</v>
+        <v>128284856</v>
       </c>
       <c r="B17" t="n">
-        <v>92757</v>
+        <v>78873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547935</v>
+        <v>547952</v>
       </c>
       <c r="R17" t="n">
-        <v>6960188</v>
+        <v>6960362</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2413,7 +2423,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2433,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2438,57 +2448,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128277049</v>
+        <v>128277304</v>
       </c>
       <c r="B18" t="n">
-        <v>92757</v>
+        <v>78873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547985</v>
+        <v>547936</v>
       </c>
       <c r="R18" t="n">
-        <v>6960231</v>
+        <v>6960173</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,7 +2530,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2540,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,10 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128273826</v>
+        <v>128274594</v>
       </c>
       <c r="B19" t="n">
-        <v>57689</v>
+        <v>80221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,39 +2578,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547957</v>
+        <v>548040</v>
       </c>
       <c r="R19" t="n">
-        <v>6960424</v>
+        <v>6960306</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2637,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,12 +2647,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,45 +2674,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128274743</v>
+        <v>128277456</v>
       </c>
       <c r="B20" t="n">
-        <v>80194</v>
+        <v>92784</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548016</v>
+        <v>547921</v>
       </c>
       <c r="R20" t="n">
-        <v>6960300</v>
+        <v>6960179</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2769,57 +2769,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128277456</v>
+        <v>128274743</v>
       </c>
       <c r="B21" t="n">
-        <v>92757</v>
+        <v>80221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547921</v>
+        <v>548016</v>
       </c>
       <c r="R21" t="n">
-        <v>6960179</v>
+        <v>6960300</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2876,22 +2876,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128274886</v>
+        <v>128284854</v>
       </c>
       <c r="B22" t="n">
-        <v>80195</v>
+        <v>78874</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,37 +2899,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548022</v>
+        <v>547936</v>
       </c>
       <c r="R22" t="n">
-        <v>6960304</v>
+        <v>6960436</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2983,22 +2983,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128277198</v>
+        <v>128274886</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>80222</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,39 +3006,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547970</v>
+        <v>548022</v>
       </c>
       <c r="R23" t="n">
-        <v>6960207</v>
+        <v>6960304</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3068,14 +3063,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,22 +3090,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128284854</v>
+        <v>128277198</v>
       </c>
       <c r="B24" t="n">
-        <v>78847</v>
+        <v>57716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,37 +3113,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547936</v>
+        <v>547970</v>
       </c>
       <c r="R24" t="n">
-        <v>6960436</v>
+        <v>6960207</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3170,19 +3175,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:56</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3197,12 +3197,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3212,7 +3212,7 @@
         <v>128275378</v>
       </c>
       <c r="B25" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>128273858</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>128278609</v>
       </c>
       <c r="B27" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128273941</v>
       </c>
       <c r="B28" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3631,49 +3631,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128275283</v>
+        <v>128274393</v>
       </c>
       <c r="B29" t="n">
-        <v>98592</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547999</v>
+        <v>547975</v>
       </c>
       <c r="R29" t="n">
-        <v>6960288</v>
+        <v>6960341</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3705,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3715,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3742,10 +3738,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128274393</v>
+        <v>128276953</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>92778</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3753,34 +3749,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547975</v>
+        <v>548012</v>
       </c>
       <c r="R30" t="n">
-        <v>6960341</v>
+        <v>6960292</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3810,19 +3806,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3837,22 +3823,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128276953</v>
+        <v>128274501</v>
       </c>
       <c r="B31" t="n">
-        <v>92751</v>
+        <v>57716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3860,34 +3846,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548012</v>
+        <v>547975</v>
       </c>
       <c r="R31" t="n">
-        <v>6960292</v>
+        <v>6960313</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3946,50 +3937,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128274501</v>
+        <v>128275283</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>98619</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547975</v>
+        <v>547999</v>
       </c>
       <c r="R32" t="n">
-        <v>6960313</v>
+        <v>6960288</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4019,9 +4009,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,61 +4036,61 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128277337</v>
+        <v>128274383</v>
       </c>
       <c r="B33" t="n">
-        <v>98592</v>
+        <v>92784</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547930</v>
+        <v>547964</v>
       </c>
       <c r="R33" t="n">
-        <v>6960191</v>
+        <v>6960346</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4120,19 +4120,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4147,49 +4137,49 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128277041</v>
+        <v>128277264</v>
       </c>
       <c r="B34" t="n">
-        <v>98592</v>
+        <v>80250</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4198,10 +4188,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547984</v>
+        <v>547947</v>
       </c>
       <c r="R34" t="n">
-        <v>6960265</v>
+        <v>6960412</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4233,7 +4223,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4243,7 +4233,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4254,16 +4244,41 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4273,7 +4288,7 @@
         <v>128274414</v>
       </c>
       <c r="B35" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,37 +4396,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128277264</v>
+        <v>128277041</v>
       </c>
       <c r="B36" t="n">
-        <v>80223</v>
+        <v>98619</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4420,10 +4435,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547947</v>
+        <v>547984</v>
       </c>
       <c r="R36" t="n">
-        <v>6960412</v>
+        <v>6960265</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4455,7 +4470,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4465,7 +4480,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4476,90 +4491,65 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128274383</v>
+        <v>128277337</v>
       </c>
       <c r="B37" t="n">
-        <v>92757</v>
+        <v>98619</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547964</v>
+        <v>547930</v>
       </c>
       <c r="R37" t="n">
-        <v>6960346</v>
+        <v>6960191</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4589,9 +4579,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4606,12 +4606,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4621,7 +4621,7 @@
         <v>128274387</v>
       </c>
       <c r="B38" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128278639</v>
+        <v>128274698</v>
       </c>
       <c r="B39" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4774,13 +4774,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>547947</v>
+        <v>547997</v>
       </c>
       <c r="R39" t="n">
-        <v>6960412</v>
+        <v>6960315</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4830,31 +4830,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128274698</v>
+        <v>128278639</v>
       </c>
       <c r="B40" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4881,7 +4876,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>36</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4890,13 +4885,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547997</v>
+        <v>547947</v>
       </c>
       <c r="R40" t="n">
-        <v>6960315</v>
+        <v>6960412</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4925,7 +4920,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4935,7 +4930,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4946,16 +4941,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4965,7 +4965,7 @@
         <v>128274742</v>
       </c>
       <c r="B41" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>128277134</v>
       </c>
       <c r="B42" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5180,10 +5180,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128273967</v>
+        <v>128274083</v>
       </c>
       <c r="B43" t="n">
-        <v>80194</v>
+        <v>57716</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5191,34 +5191,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547969</v>
+        <v>547956</v>
       </c>
       <c r="R43" t="n">
-        <v>6960411</v>
+        <v>6960372</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5251,6 +5256,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5277,10 +5287,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128274466</v>
+        <v>128273967</v>
       </c>
       <c r="B44" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5308,14 +5318,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548066</v>
+        <v>547969</v>
       </c>
       <c r="R44" t="n">
-        <v>6960351</v>
+        <v>6960411</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5345,19 +5355,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5372,22 +5372,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128274083</v>
+        <v>128274466</v>
       </c>
       <c r="B45" t="n">
-        <v>57689</v>
+        <v>80221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5395,39 +5395,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547956</v>
+        <v>548066</v>
       </c>
       <c r="R45" t="n">
-        <v>6960372</v>
+        <v>6960351</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5457,14 +5452,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5479,12 +5479,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5494,7 +5494,7 @@
         <v>128277422</v>
       </c>
       <c r="B46" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,38 +5593,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128276966</v>
+        <v>128274007</v>
       </c>
       <c r="B47" t="n">
-        <v>57689</v>
+        <v>98619</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5633,10 +5632,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548010</v>
+        <v>547955</v>
       </c>
       <c r="R47" t="n">
-        <v>6960276</v>
+        <v>6960412</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5668,7 +5667,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5678,12 +5677,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5698,49 +5692,50 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128274007</v>
+        <v>128276966</v>
       </c>
       <c r="B48" t="n">
-        <v>98592</v>
+        <v>57716</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5749,10 +5744,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547955</v>
+        <v>548010</v>
       </c>
       <c r="R48" t="n">
-        <v>6960412</v>
+        <v>6960276</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5784,7 +5779,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5794,7 +5789,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5809,12 +5809,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5824,7 +5824,7 @@
         <v>128277116</v>
       </c>
       <c r="B49" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128274041</v>
       </c>
       <c r="B50" t="n">
-        <v>80222</v>
+        <v>80249</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6025,52 +6025,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128277370</v>
+        <v>128284858</v>
       </c>
       <c r="B51" t="n">
-        <v>98592</v>
+        <v>80221</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547938</v>
+        <v>547979</v>
       </c>
       <c r="R51" t="n">
-        <v>6960182</v>
+        <v>6960273</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6099,7 +6095,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6109,7 +6105,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6124,60 +6120,64 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128284858</v>
+        <v>128277370</v>
       </c>
       <c r="B52" t="n">
-        <v>80194</v>
+        <v>98619</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547979</v>
+        <v>547938</v>
       </c>
       <c r="R52" t="n">
-        <v>6960273</v>
+        <v>6960182</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6231,12 +6231,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -2022,7 +2022,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128277049</v>
+        <v>128277341</v>
       </c>
       <c r="B14" t="n">
         <v>92784</v>
@@ -2053,14 +2053,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547985</v>
+        <v>547935</v>
       </c>
       <c r="R14" t="n">
-        <v>6960231</v>
+        <v>6960188</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,19 +2117,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128277341</v>
+        <v>128277049</v>
       </c>
       <c r="B15" t="n">
         <v>92784</v>
@@ -2160,14 +2160,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547935</v>
+        <v>547985</v>
       </c>
       <c r="R15" t="n">
-        <v>6960188</v>
+        <v>6960231</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,22 +2224,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128273826</v>
+        <v>128284856</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>78873</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,42 +2247,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547957</v>
+        <v>547952</v>
       </c>
       <c r="R16" t="n">
-        <v>6960424</v>
+        <v>6960362</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2311,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2321,12 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,19 +2331,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128284856</v>
+        <v>128277304</v>
       </c>
       <c r="B17" t="n">
         <v>78873</v>
@@ -2384,17 +2374,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547952</v>
+        <v>547936</v>
       </c>
       <c r="R17" t="n">
-        <v>6960362</v>
+        <v>6960173</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2423,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2433,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2448,22 +2438,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128277304</v>
+        <v>128274594</v>
       </c>
       <c r="B18" t="n">
-        <v>78873</v>
+        <v>80221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,34 +2461,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547936</v>
+        <v>548040</v>
       </c>
       <c r="R18" t="n">
-        <v>6960173</v>
+        <v>6960306</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2530,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2540,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2555,22 +2545,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128274594</v>
+        <v>128273826</v>
       </c>
       <c r="B19" t="n">
-        <v>80221</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,34 +2568,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548040</v>
+        <v>547957</v>
       </c>
       <c r="R19" t="n">
-        <v>6960306</v>
+        <v>6960424</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2637,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2647,7 +2642,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,45 +2674,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128277456</v>
+        <v>128274743</v>
       </c>
       <c r="B20" t="n">
-        <v>92784</v>
+        <v>80221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547921</v>
+        <v>548016</v>
       </c>
       <c r="R20" t="n">
-        <v>6960179</v>
+        <v>6960300</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2769,57 +2769,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128274743</v>
+        <v>128277456</v>
       </c>
       <c r="B21" t="n">
-        <v>80221</v>
+        <v>92784</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548016</v>
+        <v>547921</v>
       </c>
       <c r="R21" t="n">
-        <v>6960300</v>
+        <v>6960179</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2876,22 +2876,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128284854</v>
+        <v>128277198</v>
       </c>
       <c r="B22" t="n">
-        <v>78874</v>
+        <v>57716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,37 +2899,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547936</v>
+        <v>547970</v>
       </c>
       <c r="R22" t="n">
-        <v>6960436</v>
+        <v>6960207</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2956,19 +2961,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:56</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2983,12 +2983,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3102,10 +3102,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128277198</v>
+        <v>128284854</v>
       </c>
       <c r="B24" t="n">
-        <v>57716</v>
+        <v>78874</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,42 +3113,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547970</v>
+        <v>547936</v>
       </c>
       <c r="R24" t="n">
-        <v>6960207</v>
+        <v>6960436</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3175,14 +3170,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3197,12 +3197,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3631,45 +3631,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128274393</v>
+        <v>128275283</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>98619</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547975</v>
+        <v>547999</v>
       </c>
       <c r="R29" t="n">
-        <v>6960341</v>
+        <v>6960288</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3705,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3715,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,10 +3742,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128276953</v>
+        <v>128274501</v>
       </c>
       <c r="B30" t="n">
-        <v>92778</v>
+        <v>57716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,34 +3753,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548012</v>
+        <v>547975</v>
       </c>
       <c r="R30" t="n">
-        <v>6960292</v>
+        <v>6960313</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3835,10 +3844,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128274501</v>
+        <v>128276953</v>
       </c>
       <c r="B31" t="n">
-        <v>57716</v>
+        <v>92778</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3846,39 +3855,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>547975</v>
+        <v>548012</v>
       </c>
       <c r="R31" t="n">
-        <v>6960313</v>
+        <v>6960292</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3937,49 +3941,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128275283</v>
+        <v>128274393</v>
       </c>
       <c r="B32" t="n">
-        <v>98619</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547999</v>
+        <v>547975</v>
       </c>
       <c r="R32" t="n">
-        <v>6960288</v>
+        <v>6960341</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4618,38 +4618,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128274387</v>
+        <v>128274698</v>
       </c>
       <c r="B38" t="n">
-        <v>57716</v>
+        <v>98619</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4658,10 +4657,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548056</v>
+        <v>547997</v>
       </c>
       <c r="R38" t="n">
-        <v>6960360</v>
+        <v>6960315</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4693,7 +4692,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4703,12 +4702,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4723,19 +4717,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128274698</v>
+        <v>128278639</v>
       </c>
       <c r="B39" t="n">
         <v>98619</v>
@@ -4765,7 +4759,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>36</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4774,13 +4768,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>547997</v>
+        <v>547947</v>
       </c>
       <c r="R39" t="n">
-        <v>6960315</v>
+        <v>6960412</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4809,7 +4803,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4819,7 +4813,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4830,53 +4824,59 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128278639</v>
+        <v>128274387</v>
       </c>
       <c r="B40" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>36</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4885,13 +4885,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547947</v>
+        <v>548056</v>
       </c>
       <c r="R40" t="n">
-        <v>6960412</v>
+        <v>6960360</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4930,7 +4930,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4941,21 +4946,16 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5069,49 +5069,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128277134</v>
+        <v>128273967</v>
       </c>
       <c r="B42" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>547979</v>
+        <v>547969</v>
       </c>
       <c r="R42" t="n">
-        <v>6960221</v>
+        <v>6960411</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5141,19 +5137,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5168,22 +5154,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128274083</v>
+        <v>128274466</v>
       </c>
       <c r="B43" t="n">
-        <v>57716</v>
+        <v>80221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5191,39 +5177,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547956</v>
+        <v>548066</v>
       </c>
       <c r="R43" t="n">
-        <v>6960372</v>
+        <v>6960351</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5253,14 +5234,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5275,22 +5261,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128273967</v>
+        <v>128274083</v>
       </c>
       <c r="B44" t="n">
-        <v>80221</v>
+        <v>57716</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5298,34 +5284,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547969</v>
+        <v>547956</v>
       </c>
       <c r="R44" t="n">
-        <v>6960411</v>
+        <v>6960372</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5358,6 +5349,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5384,45 +5380,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128274466</v>
+        <v>128277134</v>
       </c>
       <c r="B45" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548066</v>
+        <v>547979</v>
       </c>
       <c r="R45" t="n">
-        <v>6960351</v>
+        <v>6960221</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5479,12 +5479,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6246,7 +6246,7 @@
         <v>128622880</v>
       </c>
       <c r="B53" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>128622889</v>
       </c>
       <c r="B54" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>128622885</v>
       </c>
       <c r="B55" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>128622891</v>
       </c>
       <c r="B56" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128622887</v>
       </c>
       <c r="B57" t="n">
-        <v>81101</v>
+        <v>81105</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128622888</v>
       </c>
       <c r="B58" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>128277379</v>
       </c>
       <c r="B9" t="n">
-        <v>98653</v>
+        <v>98666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>128274290</v>
       </c>
       <c r="B10" t="n">
-        <v>96738</v>
+        <v>96751</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>128284855</v>
       </c>
       <c r="B11" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>128274521</v>
       </c>
       <c r="B12" t="n">
-        <v>75196</v>
+        <v>75197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2022,32 +2022,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128277341</v>
+        <v>128277304</v>
       </c>
       <c r="B14" t="n">
-        <v>92784</v>
+        <v>78877</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547935</v>
+        <v>547936</v>
       </c>
       <c r="R14" t="n">
-        <v>6960188</v>
+        <v>6960173</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,60 +2117,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128277049</v>
+        <v>128284856</v>
       </c>
       <c r="B15" t="n">
-        <v>92784</v>
+        <v>78877</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547985</v>
+        <v>547952</v>
       </c>
       <c r="R15" t="n">
-        <v>6960231</v>
+        <v>6960362</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,60 +2224,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128284856</v>
+        <v>128277341</v>
       </c>
       <c r="B16" t="n">
-        <v>78873</v>
+        <v>92794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547952</v>
+        <v>547935</v>
       </c>
       <c r="R16" t="n">
-        <v>6960362</v>
+        <v>6960188</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2331,57 +2331,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128277304</v>
+        <v>128277049</v>
       </c>
       <c r="B17" t="n">
-        <v>78873</v>
+        <v>92794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547936</v>
+        <v>547985</v>
       </c>
       <c r="R17" t="n">
-        <v>6960173</v>
+        <v>6960231</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2453,7 +2453,7 @@
         <v>128274594</v>
       </c>
       <c r="B18" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>128274743</v>
       </c>
       <c r="B20" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>128277456</v>
       </c>
       <c r="B21" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128277198</v>
+        <v>128274886</v>
       </c>
       <c r="B22" t="n">
-        <v>57716</v>
+        <v>80226</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,39 +2899,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547970</v>
+        <v>548022</v>
       </c>
       <c r="R22" t="n">
-        <v>6960207</v>
+        <v>6960304</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2961,14 +2956,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2983,22 +2983,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128274886</v>
+        <v>128277198</v>
       </c>
       <c r="B23" t="n">
-        <v>80222</v>
+        <v>57716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,34 +3006,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548022</v>
+        <v>547970</v>
       </c>
       <c r="R23" t="n">
-        <v>6960304</v>
+        <v>6960207</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3063,19 +3068,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:46</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,12 +3090,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
         <v>128284854</v>
       </c>
       <c r="B24" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3209,37 +3209,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128275378</v>
+        <v>128273858</v>
       </c>
       <c r="B25" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3248,10 +3249,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548012</v>
+        <v>547952</v>
       </c>
       <c r="R25" t="n">
-        <v>6960292</v>
+        <v>6960420</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3284,6 +3285,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3310,38 +3316,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128273858</v>
+        <v>128275378</v>
       </c>
       <c r="B26" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3350,10 +3355,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547952</v>
+        <v>548012</v>
       </c>
       <c r="R26" t="n">
-        <v>6960420</v>
+        <v>6960292</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3386,11 +3391,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3420,7 +3420,7 @@
         <v>128278609</v>
       </c>
       <c r="B27" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128273941</v>
       </c>
       <c r="B28" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3631,49 +3631,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128275283</v>
+        <v>128274393</v>
       </c>
       <c r="B29" t="n">
-        <v>98619</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547999</v>
+        <v>547975</v>
       </c>
       <c r="R29" t="n">
-        <v>6960288</v>
+        <v>6960341</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3705,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3715,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3742,10 +3738,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128274501</v>
+        <v>128276953</v>
       </c>
       <c r="B30" t="n">
-        <v>57716</v>
+        <v>92788</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3753,39 +3749,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547975</v>
+        <v>548012</v>
       </c>
       <c r="R30" t="n">
-        <v>6960313</v>
+        <v>6960292</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3844,45 +3835,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128276953</v>
+        <v>128275283</v>
       </c>
       <c r="B31" t="n">
-        <v>92778</v>
+        <v>98632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548012</v>
+        <v>547999</v>
       </c>
       <c r="R31" t="n">
-        <v>6960292</v>
+        <v>6960288</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,9 +3907,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3929,22 +3934,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128274393</v>
+        <v>128274501</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3952,34 +3957,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
         <v>547975</v>
       </c>
       <c r="R32" t="n">
-        <v>6960341</v>
+        <v>6960313</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4009,19 +4019,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,22 +4036,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128274383</v>
+        <v>128277264</v>
       </c>
       <c r="B33" t="n">
-        <v>92784</v>
+        <v>80254</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4059,41 +4059,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547964</v>
+        <v>547947</v>
       </c>
       <c r="R33" t="n">
-        <v>6960346</v>
+        <v>6960412</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4120,11 +4120,21 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4133,26 +4143,51 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128277264</v>
+        <v>128274383</v>
       </c>
       <c r="B34" t="n">
-        <v>80250</v>
+        <v>92794</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4160,41 +4195,41 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547947</v>
+        <v>547964</v>
       </c>
       <c r="R34" t="n">
-        <v>6960412</v>
+        <v>6960346</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4221,21 +4256,11 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4244,51 +4269,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128274414</v>
+        <v>128277337</v>
       </c>
       <c r="B35" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4315,22 +4315,22 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547966</v>
+        <v>547930</v>
       </c>
       <c r="R35" t="n">
-        <v>6960356</v>
+        <v>6960191</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4384,12 +4384,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4399,7 +4399,7 @@
         <v>128277041</v>
       </c>
       <c r="B36" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4507,10 +4507,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128277337</v>
+        <v>128274414</v>
       </c>
       <c r="B37" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4537,22 +4537,22 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547930</v>
+        <v>547966</v>
       </c>
       <c r="R37" t="n">
-        <v>6960191</v>
+        <v>6960356</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4606,49 +4606,50 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128274698</v>
+        <v>128274387</v>
       </c>
       <c r="B38" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4657,10 +4658,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>547997</v>
+        <v>548056</v>
       </c>
       <c r="R38" t="n">
-        <v>6960315</v>
+        <v>6960360</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4692,7 +4693,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4702,7 +4703,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4717,12 +4723,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4732,7 +4738,7 @@
         <v>128278639</v>
       </c>
       <c r="B39" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4845,38 +4851,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128274387</v>
+        <v>128274698</v>
       </c>
       <c r="B40" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4885,10 +4890,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548056</v>
+        <v>547997</v>
       </c>
       <c r="R40" t="n">
-        <v>6960360</v>
+        <v>6960315</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4920,7 +4925,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4930,12 +4935,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4950,12 +4950,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4965,7 +4965,7 @@
         <v>128274742</v>
       </c>
       <c r="B41" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>128273967</v>
       </c>
       <c r="B42" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>128274466</v>
       </c>
       <c r="B43" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>128277134</v>
       </c>
       <c r="B45" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>128274007</v>
       </c>
       <c r="B47" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>128277116</v>
       </c>
       <c r="B49" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128274041</v>
       </c>
       <c r="B50" t="n">
-        <v>80249</v>
+        <v>80253</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6025,48 +6025,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128284858</v>
+        <v>128277370</v>
       </c>
       <c r="B51" t="n">
-        <v>80221</v>
+        <v>98632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547979</v>
+        <v>547938</v>
       </c>
       <c r="R51" t="n">
-        <v>6960273</v>
+        <v>6960182</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6095,7 +6099,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6105,7 +6109,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6120,64 +6124,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128277370</v>
+        <v>128284858</v>
       </c>
       <c r="B52" t="n">
-        <v>98619</v>
+        <v>80225</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547938</v>
+        <v>547979</v>
       </c>
       <c r="R52" t="n">
-        <v>6960182</v>
+        <v>6960273</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6231,12 +6231,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6343,7 +6343,7 @@
         <v>128622889</v>
       </c>
       <c r="B54" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>128622891</v>
       </c>
       <c r="B56" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -2022,32 +2022,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128277304</v>
+        <v>128277341</v>
       </c>
       <c r="B14" t="n">
-        <v>78877</v>
+        <v>92794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547936</v>
+        <v>547935</v>
       </c>
       <c r="R14" t="n">
-        <v>6960173</v>
+        <v>6960188</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,60 +2117,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128284856</v>
+        <v>128277049</v>
       </c>
       <c r="B15" t="n">
-        <v>78877</v>
+        <v>92794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547952</v>
+        <v>547985</v>
       </c>
       <c r="R15" t="n">
-        <v>6960362</v>
+        <v>6960231</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,57 +2224,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128277341</v>
+        <v>128274594</v>
       </c>
       <c r="B16" t="n">
-        <v>92794</v>
+        <v>80225</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547935</v>
+        <v>548040</v>
       </c>
       <c r="R16" t="n">
-        <v>6960188</v>
+        <v>6960306</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,48 +2343,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128277049</v>
+        <v>128284856</v>
       </c>
       <c r="B17" t="n">
-        <v>92794</v>
+        <v>78877</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547985</v>
+        <v>547952</v>
       </c>
       <c r="R17" t="n">
-        <v>6960231</v>
+        <v>6960362</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2438,22 +2438,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128274594</v>
+        <v>128277304</v>
       </c>
       <c r="B18" t="n">
-        <v>80225</v>
+        <v>78877</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,34 +2461,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548040</v>
+        <v>547936</v>
       </c>
       <c r="R18" t="n">
-        <v>6960306</v>
+        <v>6960173</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,12 +2545,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2674,45 +2674,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128274743</v>
+        <v>128277456</v>
       </c>
       <c r="B20" t="n">
-        <v>80225</v>
+        <v>92794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548016</v>
+        <v>547921</v>
       </c>
       <c r="R20" t="n">
-        <v>6960300</v>
+        <v>6960179</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2769,57 +2769,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128277456</v>
+        <v>128274743</v>
       </c>
       <c r="B21" t="n">
-        <v>92794</v>
+        <v>80225</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547921</v>
+        <v>548016</v>
       </c>
       <c r="R21" t="n">
-        <v>6960179</v>
+        <v>6960300</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2876,12 +2876,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128277198</v>
+        <v>128284854</v>
       </c>
       <c r="B23" t="n">
-        <v>57716</v>
+        <v>78878</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,42 +3006,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547970</v>
+        <v>547936</v>
       </c>
       <c r="R23" t="n">
-        <v>6960207</v>
+        <v>6960436</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3068,14 +3063,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,22 +3090,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128284854</v>
+        <v>128277198</v>
       </c>
       <c r="B24" t="n">
-        <v>78878</v>
+        <v>57716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,37 +3113,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547936</v>
+        <v>547970</v>
       </c>
       <c r="R24" t="n">
-        <v>6960436</v>
+        <v>6960207</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3170,19 +3175,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:56</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3197,50 +3197,49 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128273858</v>
+        <v>128275378</v>
       </c>
       <c r="B25" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3249,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547952</v>
+        <v>548012</v>
       </c>
       <c r="R25" t="n">
-        <v>6960420</v>
+        <v>6960292</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3285,11 +3284,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3316,37 +3310,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128275378</v>
+        <v>128273858</v>
       </c>
       <c r="B26" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3355,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548012</v>
+        <v>547952</v>
       </c>
       <c r="R26" t="n">
-        <v>6960292</v>
+        <v>6960420</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3391,6 +3386,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3631,45 +3631,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128274393</v>
+        <v>128275283</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547975</v>
+        <v>547999</v>
       </c>
       <c r="R29" t="n">
-        <v>6960341</v>
+        <v>6960288</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3705,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3715,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3835,49 +3839,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128275283</v>
+        <v>128274393</v>
       </c>
       <c r="B31" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>547999</v>
+        <v>547975</v>
       </c>
       <c r="R31" t="n">
-        <v>6960288</v>
+        <v>6960341</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4184,52 +4184,52 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128274383</v>
+        <v>128274414</v>
       </c>
       <c r="B34" t="n">
-        <v>92794</v>
+        <v>98632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547964</v>
+        <v>547966</v>
       </c>
       <c r="R34" t="n">
-        <v>6960346</v>
+        <v>6960356</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4256,9 +4256,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4273,19 +4283,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128277337</v>
+        <v>128277041</v>
       </c>
       <c r="B35" t="n">
         <v>98632</v>
@@ -4315,22 +4325,22 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547930</v>
+        <v>547984</v>
       </c>
       <c r="R35" t="n">
-        <v>6960191</v>
+        <v>6960265</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4359,7 +4369,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4369,7 +4379,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4384,19 +4394,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128277041</v>
+        <v>128277337</v>
       </c>
       <c r="B36" t="n">
         <v>98632</v>
@@ -4426,22 +4436,22 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547984</v>
+        <v>547930</v>
       </c>
       <c r="R36" t="n">
-        <v>6960265</v>
+        <v>6960191</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4470,7 +4480,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4480,7 +4490,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4495,64 +4505,64 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128274414</v>
+        <v>128274383</v>
       </c>
       <c r="B37" t="n">
-        <v>98632</v>
+        <v>92794</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547966</v>
+        <v>547964</v>
       </c>
       <c r="R37" t="n">
-        <v>6960356</v>
+        <v>6960346</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4579,19 +4589,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4606,12 +4606,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4735,7 +4735,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128278639</v>
+        <v>128274698</v>
       </c>
       <c r="B39" t="n">
         <v>98632</v>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4774,13 +4774,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>547947</v>
+        <v>547997</v>
       </c>
       <c r="R39" t="n">
-        <v>6960412</v>
+        <v>6960315</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4830,28 +4830,23 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128274698</v>
+        <v>128278639</v>
       </c>
       <c r="B40" t="n">
         <v>98632</v>
@@ -4881,7 +4876,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>36</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4890,13 +4885,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547997</v>
+        <v>547947</v>
       </c>
       <c r="R40" t="n">
-        <v>6960315</v>
+        <v>6960412</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4925,7 +4920,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4935,7 +4930,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4946,16 +4941,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5593,37 +5593,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128274007</v>
+        <v>128276966</v>
       </c>
       <c r="B47" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5632,10 +5633,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547955</v>
+        <v>548010</v>
       </c>
       <c r="R47" t="n">
-        <v>6960412</v>
+        <v>6960276</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5667,7 +5668,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5677,7 +5678,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5692,50 +5698,49 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128276966</v>
+        <v>128274007</v>
       </c>
       <c r="B48" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5744,10 +5749,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548010</v>
+        <v>547955</v>
       </c>
       <c r="R48" t="n">
-        <v>6960276</v>
+        <v>6960412</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5779,7 +5784,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5789,12 +5794,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5809,57 +5809,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128277116</v>
+        <v>128274041</v>
       </c>
       <c r="B49" t="n">
-        <v>80225</v>
+        <v>80253</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>547993</v>
+        <v>547977</v>
       </c>
       <c r="R49" t="n">
-        <v>6960206</v>
+        <v>6960396</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5889,19 +5889,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5916,57 +5906,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128274041</v>
+        <v>128277116</v>
       </c>
       <c r="B50" t="n">
-        <v>80253</v>
+        <v>80225</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547977</v>
+        <v>547993</v>
       </c>
       <c r="R50" t="n">
-        <v>6960396</v>
+        <v>6960206</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,9 +5986,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6013,12 +6013,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -2888,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128274886</v>
+        <v>128284854</v>
       </c>
       <c r="B22" t="n">
-        <v>80226</v>
+        <v>78878</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,37 +2899,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548022</v>
+        <v>547936</v>
       </c>
       <c r="R22" t="n">
-        <v>6960304</v>
+        <v>6960436</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2983,22 +2983,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128284854</v>
+        <v>128274886</v>
       </c>
       <c r="B23" t="n">
-        <v>78878</v>
+        <v>80226</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,37 +3006,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Mörttjärnen, Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547936</v>
+        <v>548022</v>
       </c>
       <c r="R23" t="n">
-        <v>6960436</v>
+        <v>6960304</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,12 +3090,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -6246,7 +6246,7 @@
         <v>128622880</v>
       </c>
       <c r="B53" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>128622889</v>
       </c>
       <c r="B54" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>128622885</v>
       </c>
       <c r="B55" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>128622891</v>
       </c>
       <c r="B56" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128622887</v>
       </c>
       <c r="B57" t="n">
-        <v>81105</v>
+        <v>81109</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128622888</v>
       </c>
       <c r="B58" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -6246,7 +6246,7 @@
         <v>128622880</v>
       </c>
       <c r="B53" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>128622889</v>
       </c>
       <c r="B54" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>128622885</v>
       </c>
       <c r="B55" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>128622891</v>
       </c>
       <c r="B56" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128622887</v>
       </c>
       <c r="B57" t="n">
-        <v>81109</v>
+        <v>81014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128622888</v>
       </c>
       <c r="B58" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -6246,7 +6246,7 @@
         <v>128622880</v>
       </c>
       <c r="B53" t="n">
-        <v>79648</v>
+        <v>79653</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>128622889</v>
       </c>
       <c r="B54" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>128622885</v>
       </c>
       <c r="B55" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>128622891</v>
       </c>
       <c r="B56" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128622887</v>
       </c>
       <c r="B57" t="n">
-        <v>81014</v>
+        <v>81019</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128622888</v>
       </c>
       <c r="B58" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 28601-2021 artfynd.xlsx
+++ b/artfynd/A 28601-2021 artfynd.xlsx
@@ -6246,7 +6246,7 @@
         <v>128622880</v>
       </c>
       <c r="B53" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>128622889</v>
       </c>
       <c r="B54" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>128622885</v>
       </c>
       <c r="B55" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>128622891</v>
       </c>
       <c r="B56" t="n">
-        <v>92805</v>
+        <v>92813</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>128622887</v>
       </c>
       <c r="B57" t="n">
-        <v>81019</v>
+        <v>81020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128622888</v>
       </c>
       <c r="B58" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
